--- a/output/model_analysis_20260429/cross_model_bin_pivot_rate_only.xlsx
+++ b/output/model_analysis_20260429/cross_model_bin_pivot_rate_only.xlsx
@@ -1142,7 +1142,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F62"/>
+  <dimension ref="A1:E62"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="25" customWidth="1" min="1" max="1"/>
@@ -1150,7 +1150,6 @@
     <col width="10" customWidth="1" min="3" max="3"/>
     <col width="10" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
-    <col width="10" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1183,11 +1182,6 @@
       </c>
       <c r="E2" s="1" t="inlineStr">
         <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="F2" s="1" t="inlineStr">
-        <is>
           <t>Total</t>
         </is>
       </c>
@@ -1200,27 +1194,22 @@
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>2,783</t>
+          <t>25</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>1,466</t>
+          <t>3</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>397</t>
-        </is>
-      </c>
-      <c r="E3" s="2" t="inlineStr">
-        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="F3" s="4" t="inlineStr">
-        <is>
-          <t>4,647</t>
+      <c r="E3" s="4" t="inlineStr">
+        <is>
+          <t>29</t>
         </is>
       </c>
     </row>
@@ -1232,27 +1221,22 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>1,473</t>
+          <t>13</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>2,479</t>
+          <t>16</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>1,136</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F4" s="4" t="inlineStr">
-        <is>
-          <t>5,088</t>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="E4" s="4" t="inlineStr">
+        <is>
+          <t>35</t>
         </is>
       </c>
     </row>
@@ -1264,27 +1248,22 @@
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>178</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>900</t>
+          <t>11</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>1,536</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="F5" s="4" t="inlineStr">
-        <is>
-          <t>2,615</t>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E5" s="4" t="inlineStr">
+        <is>
+          <t>22</t>
         </is>
       </c>
     </row>
@@ -1296,27 +1275,22 @@
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>4,434</t>
+          <t>39</t>
         </is>
       </c>
       <c r="C6" s="4" t="inlineStr">
         <is>
-          <t>4,845</t>
+          <t>30</t>
         </is>
       </c>
       <c r="D6" s="4" t="inlineStr">
         <is>
-          <t>3,069</t>
+          <t>17</t>
         </is>
       </c>
       <c r="E6" s="4" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="F6" s="4" t="inlineStr">
-        <is>
-          <t>12,350</t>
+          <t>86</t>
         </is>
       </c>
     </row>
@@ -1352,11 +1326,6 @@
       </c>
       <c r="E10" s="1" t="inlineStr">
         <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="F10" s="1" t="inlineStr">
-        <is>
           <t>Total</t>
         </is>
       </c>
@@ -1369,27 +1338,22 @@
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>168</t>
+          <t>0</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>163</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>49</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F11" s="4" t="inlineStr">
-        <is>
-          <t>380</t>
+      <c r="E11" s="4" t="inlineStr">
+        <is>
+          <t>0</t>
         </is>
       </c>
     </row>
@@ -1401,27 +1365,22 @@
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>119</t>
+          <t>0</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>330</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>211</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F12" s="4" t="inlineStr">
-        <is>
-          <t>660</t>
+      <c r="E12" s="4" t="inlineStr">
+        <is>
+          <t>2</t>
         </is>
       </c>
     </row>
@@ -1433,27 +1392,22 @@
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>0</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>160</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>411</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F13" s="4" t="inlineStr">
-        <is>
-          <t>589</t>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E13" s="4" t="inlineStr">
+        <is>
+          <t>3</t>
         </is>
       </c>
     </row>
@@ -1465,27 +1419,22 @@
       </c>
       <c r="B14" s="4" t="inlineStr">
         <is>
-          <t>305</t>
+          <t>0</t>
         </is>
       </c>
       <c r="C14" s="4" t="inlineStr">
         <is>
-          <t>653</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D14" s="4" t="inlineStr">
         <is>
-          <t>671</t>
+          <t>3</t>
         </is>
       </c>
       <c r="E14" s="4" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F14" s="4" t="inlineStr">
-        <is>
-          <t>1,629</t>
+          <t>5</t>
         </is>
       </c>
     </row>
@@ -1521,11 +1470,6 @@
       </c>
       <c r="E18" s="1" t="inlineStr">
         <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="F18" s="1" t="inlineStr">
-        <is>
           <t>Total</t>
         </is>
       </c>
@@ -1538,27 +1482,22 @@
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>2,615</t>
+          <t>25</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>1,303</t>
+          <t>3</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>348</t>
-        </is>
-      </c>
-      <c r="E19" s="2" t="inlineStr">
-        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="F19" s="4" t="inlineStr">
-        <is>
-          <t>4,267</t>
+      <c r="E19" s="4" t="inlineStr">
+        <is>
+          <t>29</t>
         </is>
       </c>
     </row>
@@ -1570,27 +1509,22 @@
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>1,354</t>
+          <t>13</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>2,149</t>
+          <t>14</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>925</t>
-        </is>
-      </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F20" s="4" t="inlineStr">
-        <is>
-          <t>4,428</t>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="E20" s="4" t="inlineStr">
+        <is>
+          <t>33</t>
         </is>
       </c>
     </row>
@@ -1602,27 +1536,22 @@
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>160</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>740</t>
+          <t>11</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>1,125</t>
-        </is>
-      </c>
-      <c r="E21" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="F21" s="4" t="inlineStr">
-        <is>
-          <t>2,026</t>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="E21" s="4" t="inlineStr">
+        <is>
+          <t>19</t>
         </is>
       </c>
     </row>
@@ -1634,27 +1563,22 @@
       </c>
       <c r="B22" s="4" t="inlineStr">
         <is>
-          <t>4,129</t>
+          <t>39</t>
         </is>
       </c>
       <c r="C22" s="4" t="inlineStr">
         <is>
-          <t>4,192</t>
+          <t>28</t>
         </is>
       </c>
       <c r="D22" s="4" t="inlineStr">
         <is>
-          <t>2,398</t>
+          <t>14</t>
         </is>
       </c>
       <c r="E22" s="4" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="F22" s="4" t="inlineStr">
-        <is>
-          <t>10,721</t>
+          <t>81</t>
         </is>
       </c>
     </row>
@@ -1690,11 +1614,6 @@
       </c>
       <c r="E26" s="1" t="inlineStr">
         <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="F26" s="1" t="inlineStr">
-        <is>
           <t>Total</t>
         </is>
       </c>
@@ -1707,27 +1626,22 @@
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>6.04%</t>
+          <t>0.00%</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>11.12%</t>
+          <t>0.00%</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>12.34%</t>
-        </is>
-      </c>
-      <c r="E27" s="2" t="inlineStr">
-        <is>
           <t>0.00%</t>
         </is>
       </c>
-      <c r="F27" s="4" t="inlineStr">
-        <is>
-          <t>8.18%</t>
+      <c r="E27" s="4" t="inlineStr">
+        <is>
+          <t>0.00%</t>
         </is>
       </c>
     </row>
@@ -1739,23 +1653,22 @@
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>8.08%</t>
+          <t>0.00%</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>13.31%</t>
+          <t>12.50%</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>18.57%</t>
-        </is>
-      </c>
-      <c r="E28" s="2" t="inlineStr"/>
-      <c r="F28" s="4" t="inlineStr">
-        <is>
-          <t>12.97%</t>
+          <t>0.00%</t>
+        </is>
+      </c>
+      <c r="E28" s="4" t="inlineStr">
+        <is>
+          <t>5.71%</t>
         </is>
       </c>
     </row>
@@ -1767,27 +1680,22 @@
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>10.11%</t>
+          <t>0.00%</t>
         </is>
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>17.78%</t>
+          <t>0.00%</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>26.76%</t>
-        </is>
-      </c>
-      <c r="E29" s="2" t="inlineStr">
-        <is>
-          <t>0.00%</t>
-        </is>
-      </c>
-      <c r="F29" s="4" t="inlineStr">
-        <is>
-          <t>22.52%</t>
+          <t>30.00%</t>
+        </is>
+      </c>
+      <c r="E29" s="4" t="inlineStr">
+        <is>
+          <t>13.64%</t>
         </is>
       </c>
     </row>
@@ -1799,27 +1707,22 @@
       </c>
       <c r="B30" s="4" t="inlineStr">
         <is>
-          <t>6.88%</t>
+          <t>0.00%</t>
         </is>
       </c>
       <c r="C30" s="4" t="inlineStr">
         <is>
-          <t>13.48%</t>
+          <t>6.67%</t>
         </is>
       </c>
       <c r="D30" s="4" t="inlineStr">
         <is>
-          <t>21.86%</t>
+          <t>17.65%</t>
         </is>
       </c>
       <c r="E30" s="4" t="inlineStr">
         <is>
-          <t>0.00%</t>
-        </is>
-      </c>
-      <c r="F30" s="4" t="inlineStr">
-        <is>
-          <t>13.19%</t>
+          <t>5.81%</t>
         </is>
       </c>
     </row>
@@ -1855,11 +1758,6 @@
       </c>
       <c r="E34" s="1" t="inlineStr">
         <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="F34" s="1" t="inlineStr">
-        <is>
           <t>Total</t>
         </is>
       </c>
@@ -1872,27 +1770,22 @@
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>5,092</t>
+          <t>30</t>
         </is>
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>2,502</t>
+          <t>4</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>504</t>
-        </is>
-      </c>
-      <c r="E35" s="2" t="inlineStr">
-        <is>
-          <t>69</t>
-        </is>
-      </c>
-      <c r="F35" s="4" t="inlineStr">
-        <is>
-          <t>8,167</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E35" s="4" t="inlineStr">
+        <is>
+          <t>35</t>
         </is>
       </c>
     </row>
@@ -1904,27 +1797,22 @@
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>2,897</t>
+          <t>15</t>
         </is>
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>4,251</t>
+          <t>19</t>
         </is>
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>1,472</t>
-        </is>
-      </c>
-      <c r="E36" s="2" t="inlineStr">
-        <is>
-          <t>81</t>
-        </is>
-      </c>
-      <c r="F36" s="4" t="inlineStr">
-        <is>
-          <t>8,701</t>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="E36" s="4" t="inlineStr">
+        <is>
+          <t>40</t>
         </is>
       </c>
     </row>
@@ -1936,27 +1824,22 @@
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>428</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>1,777</t>
+          <t>11</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>2,011</t>
-        </is>
-      </c>
-      <c r="E37" s="2" t="inlineStr">
-        <is>
-          <t>61</t>
-        </is>
-      </c>
-      <c r="F37" s="4" t="inlineStr">
-        <is>
-          <t>4,277</t>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="E37" s="4" t="inlineStr">
+        <is>
+          <t>23</t>
         </is>
       </c>
     </row>
@@ -1968,27 +1851,22 @@
       </c>
       <c r="B38" s="4" t="inlineStr">
         <is>
-          <t>8,417</t>
+          <t>46</t>
         </is>
       </c>
       <c r="C38" s="4" t="inlineStr">
         <is>
-          <t>8,530</t>
+          <t>34</t>
         </is>
       </c>
       <c r="D38" s="4" t="inlineStr">
         <is>
-          <t>3,987</t>
+          <t>18</t>
         </is>
       </c>
       <c r="E38" s="4" t="inlineStr">
         <is>
-          <t>211</t>
-        </is>
-      </c>
-      <c r="F38" s="4" t="inlineStr">
-        <is>
-          <t>21,145</t>
+          <t>98</t>
         </is>
       </c>
     </row>
@@ -2024,11 +1902,6 @@
       </c>
       <c r="E42" s="1" t="inlineStr">
         <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="F42" s="1" t="inlineStr">
-        <is>
           <t>Total</t>
         </is>
       </c>
@@ -2041,27 +1914,22 @@
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>154</t>
+          <t>0</t>
         </is>
       </c>
       <c r="C43" s="2" t="inlineStr">
         <is>
-          <t>151</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
-          <t>47</t>
-        </is>
-      </c>
-      <c r="E43" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="F43" s="4" t="inlineStr">
-        <is>
-          <t>353</t>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E43" s="4" t="inlineStr">
+        <is>
+          <t>0</t>
         </is>
       </c>
     </row>
@@ -2073,27 +1941,22 @@
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>115</t>
+          <t>0</t>
         </is>
       </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t>339</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
-          <t>158</t>
-        </is>
-      </c>
-      <c r="E44" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="F44" s="4" t="inlineStr">
-        <is>
-          <t>618</t>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E44" s="4" t="inlineStr">
+        <is>
+          <t>1</t>
         </is>
       </c>
     </row>
@@ -2105,27 +1968,22 @@
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>0</t>
         </is>
       </c>
       <c r="C45" s="2" t="inlineStr">
         <is>
-          <t>185</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D45" s="2" t="inlineStr">
         <is>
-          <t>287</t>
-        </is>
-      </c>
-      <c r="E45" s="2" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="F45" s="4" t="inlineStr">
-        <is>
-          <t>508</t>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E45" s="4" t="inlineStr">
+        <is>
+          <t>3</t>
         </is>
       </c>
     </row>
@@ -2137,27 +1995,22 @@
       </c>
       <c r="B46" s="4" t="inlineStr">
         <is>
-          <t>298</t>
+          <t>0</t>
         </is>
       </c>
       <c r="C46" s="4" t="inlineStr">
         <is>
-          <t>675</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D46" s="4" t="inlineStr">
         <is>
-          <t>492</t>
+          <t>2</t>
         </is>
       </c>
       <c r="E46" s="4" t="inlineStr">
         <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="F46" s="4" t="inlineStr">
-        <is>
-          <t>1,479</t>
+          <t>4</t>
         </is>
       </c>
     </row>
@@ -2193,11 +2046,6 @@
       </c>
       <c r="E50" s="1" t="inlineStr">
         <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="F50" s="1" t="inlineStr">
-        <is>
           <t>Total</t>
         </is>
       </c>
@@ -2210,27 +2058,22 @@
       </c>
       <c r="B51" s="2" t="inlineStr">
         <is>
-          <t>4,938</t>
+          <t>30</t>
         </is>
       </c>
       <c r="C51" s="2" t="inlineStr">
         <is>
-          <t>2,351</t>
+          <t>4</t>
         </is>
       </c>
       <c r="D51" s="2" t="inlineStr">
         <is>
-          <t>457</t>
-        </is>
-      </c>
-      <c r="E51" s="2" t="inlineStr">
-        <is>
-          <t>68</t>
-        </is>
-      </c>
-      <c r="F51" s="4" t="inlineStr">
-        <is>
-          <t>7,814</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E51" s="4" t="inlineStr">
+        <is>
+          <t>35</t>
         </is>
       </c>
     </row>
@@ -2242,27 +2085,22 @@
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>2,782</t>
+          <t>15</t>
         </is>
       </c>
       <c r="C52" s="2" t="inlineStr">
         <is>
-          <t>3,912</t>
+          <t>18</t>
         </is>
       </c>
       <c r="D52" s="2" t="inlineStr">
         <is>
-          <t>1,314</t>
-        </is>
-      </c>
-      <c r="E52" s="2" t="inlineStr">
-        <is>
-          <t>75</t>
-        </is>
-      </c>
-      <c r="F52" s="4" t="inlineStr">
-        <is>
-          <t>8,083</t>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="E52" s="4" t="inlineStr">
+        <is>
+          <t>39</t>
         </is>
       </c>
     </row>
@@ -2274,27 +2112,22 @@
       </c>
       <c r="B53" s="2" t="inlineStr">
         <is>
-          <t>399</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C53" s="2" t="inlineStr">
         <is>
-          <t>1,592</t>
+          <t>10</t>
         </is>
       </c>
       <c r="D53" s="2" t="inlineStr">
         <is>
-          <t>1,724</t>
-        </is>
-      </c>
-      <c r="E53" s="2" t="inlineStr">
-        <is>
-          <t>54</t>
-        </is>
-      </c>
-      <c r="F53" s="4" t="inlineStr">
-        <is>
-          <t>3,769</t>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="E53" s="4" t="inlineStr">
+        <is>
+          <t>20</t>
         </is>
       </c>
     </row>
@@ -2306,27 +2139,22 @@
       </c>
       <c r="B54" s="4" t="inlineStr">
         <is>
-          <t>8,119</t>
+          <t>46</t>
         </is>
       </c>
       <c r="C54" s="4" t="inlineStr">
         <is>
-          <t>7,855</t>
+          <t>32</t>
         </is>
       </c>
       <c r="D54" s="4" t="inlineStr">
         <is>
-          <t>3,495</t>
+          <t>16</t>
         </is>
       </c>
       <c r="E54" s="4" t="inlineStr">
         <is>
-          <t>197</t>
-        </is>
-      </c>
-      <c r="F54" s="4" t="inlineStr">
-        <is>
-          <t>19,666</t>
+          <t>94</t>
         </is>
       </c>
     </row>
@@ -2362,11 +2190,6 @@
       </c>
       <c r="E58" s="1" t="inlineStr">
         <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="F58" s="1" t="inlineStr">
-        <is>
           <t>Total</t>
         </is>
       </c>
@@ -2379,27 +2202,22 @@
       </c>
       <c r="B59" s="2" t="inlineStr">
         <is>
-          <t>3.02%</t>
+          <t>0.00%</t>
         </is>
       </c>
       <c r="C59" s="2" t="inlineStr">
         <is>
-          <t>6.04%</t>
+          <t>0.00%</t>
         </is>
       </c>
       <c r="D59" s="2" t="inlineStr">
         <is>
-          <t>9.33%</t>
-        </is>
-      </c>
-      <c r="E59" s="2" t="inlineStr">
-        <is>
-          <t>1.45%</t>
-        </is>
-      </c>
-      <c r="F59" s="4" t="inlineStr">
-        <is>
-          <t>4.32%</t>
+          <t>0.00%</t>
+        </is>
+      </c>
+      <c r="E59" s="4" t="inlineStr">
+        <is>
+          <t>0.00%</t>
         </is>
       </c>
     </row>
@@ -2411,27 +2229,22 @@
       </c>
       <c r="B60" s="2" t="inlineStr">
         <is>
-          <t>3.97%</t>
+          <t>0.00%</t>
         </is>
       </c>
       <c r="C60" s="2" t="inlineStr">
         <is>
-          <t>7.97%</t>
+          <t>5.26%</t>
         </is>
       </c>
       <c r="D60" s="2" t="inlineStr">
         <is>
-          <t>10.73%</t>
-        </is>
-      </c>
-      <c r="E60" s="2" t="inlineStr">
-        <is>
-          <t>7.41%</t>
-        </is>
-      </c>
-      <c r="F60" s="4" t="inlineStr">
-        <is>
-          <t>7.10%</t>
+          <t>0.00%</t>
+        </is>
+      </c>
+      <c r="E60" s="4" t="inlineStr">
+        <is>
+          <t>2.50%</t>
         </is>
       </c>
     </row>
@@ -2443,27 +2256,22 @@
       </c>
       <c r="B61" s="2" t="inlineStr">
         <is>
-          <t>6.78%</t>
+          <t>0.00%</t>
         </is>
       </c>
       <c r="C61" s="2" t="inlineStr">
         <is>
-          <t>10.41%</t>
+          <t>9.09%</t>
         </is>
       </c>
       <c r="D61" s="2" t="inlineStr">
         <is>
-          <t>14.27%</t>
-        </is>
-      </c>
-      <c r="E61" s="2" t="inlineStr">
-        <is>
-          <t>11.48%</t>
-        </is>
-      </c>
-      <c r="F61" s="4" t="inlineStr">
-        <is>
-          <t>11.88%</t>
+          <t>18.18%</t>
+        </is>
+      </c>
+      <c r="E61" s="4" t="inlineStr">
+        <is>
+          <t>13.04%</t>
         </is>
       </c>
     </row>
@@ -2475,27 +2283,22 @@
       </c>
       <c r="B62" s="4" t="inlineStr">
         <is>
-          <t>3.54%</t>
+          <t>0.00%</t>
         </is>
       </c>
       <c r="C62" s="4" t="inlineStr">
         <is>
-          <t>7.91%</t>
+          <t>5.88%</t>
         </is>
       </c>
       <c r="D62" s="4" t="inlineStr">
         <is>
-          <t>12.34%</t>
+          <t>11.11%</t>
         </is>
       </c>
       <c r="E62" s="4" t="inlineStr">
         <is>
-          <t>6.64%</t>
-        </is>
-      </c>
-      <c r="F62" s="4" t="inlineStr">
-        <is>
-          <t>6.99%</t>
+          <t>4.08%</t>
         </is>
       </c>
     </row>
@@ -2510,15 +2313,14 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F46"/>
+  <dimension ref="A1:E46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="32" customWidth="1" min="1" max="1"/>
-    <col width="14" customWidth="1" min="2" max="2"/>
-    <col width="14" customWidth="1" min="3" max="3"/>
-    <col width="14" customWidth="1" min="4" max="4"/>
-    <col width="12" customWidth="1" min="5" max="5"/>
-    <col width="15" customWidth="1" min="6" max="6"/>
+    <col width="11" customWidth="1" min="2" max="2"/>
+    <col width="11" customWidth="1" min="3" max="3"/>
+    <col width="11" customWidth="1" min="4" max="4"/>
+    <col width="11" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2551,11 +2353,6 @@
       </c>
       <c r="E2" s="1" t="inlineStr">
         <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="F2" s="1" t="inlineStr">
-        <is>
           <t>Total</t>
         </is>
       </c>
@@ -2568,27 +2365,22 @@
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>186,061.58</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>184,144.33</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>58,785.41</t>
-        </is>
-      </c>
-      <c r="E3" s="2" t="inlineStr">
-        <is>
           <t>0.00</t>
         </is>
       </c>
-      <c r="F3" s="4" t="inlineStr">
-        <is>
-          <t>428,991.32</t>
+      <c r="E3" s="4" t="inlineStr">
+        <is>
+          <t>0.00</t>
         </is>
       </c>
     </row>
@@ -2600,27 +2392,22 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>95,551.27</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>281,608.84</t>
+          <t>2,945.06</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>183,776.86</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
           <t>0.00</t>
         </is>
       </c>
-      <c r="F4" s="4" t="inlineStr">
-        <is>
-          <t>560,936.97</t>
+      <c r="E4" s="4" t="inlineStr">
+        <is>
+          <t>2,945.06</t>
         </is>
       </c>
     </row>
@@ -2632,27 +2419,22 @@
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>11,348.85</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>105,766.69</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>275,285.61</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>0.00</t>
-        </is>
-      </c>
-      <c r="F5" s="4" t="inlineStr">
-        <is>
-          <t>392,401.15</t>
+          <t>1,495.57</t>
+        </is>
+      </c>
+      <c r="E5" s="4" t="inlineStr">
+        <is>
+          <t>1,495.57</t>
         </is>
       </c>
     </row>
@@ -2664,27 +2446,22 @@
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>292,961.70</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="C6" s="4" t="inlineStr">
         <is>
-          <t>571,519.86</t>
+          <t>2,945.06</t>
         </is>
       </c>
       <c r="D6" s="4" t="inlineStr">
         <is>
-          <t>517,847.88</t>
+          <t>1,495.57</t>
         </is>
       </c>
       <c r="E6" s="4" t="inlineStr">
         <is>
-          <t>0.00</t>
-        </is>
-      </c>
-      <c r="F6" s="4" t="inlineStr">
-        <is>
-          <t>1,382,329.44</t>
+          <t>4,440.63</t>
         </is>
       </c>
     </row>
@@ -2720,11 +2497,6 @@
       </c>
       <c r="E10" s="1" t="inlineStr">
         <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="F10" s="1" t="inlineStr">
-        <is>
           <t>Total</t>
         </is>
       </c>
@@ -2737,27 +2509,22 @@
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>6,693,900.00</t>
+          <t>33,225.00</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>2,953,295.00</t>
+          <t>3,675.00</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>674,375.00</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>109,525.00</t>
-        </is>
-      </c>
-      <c r="F11" s="4" t="inlineStr">
-        <is>
-          <t>10,431,095.00</t>
+          <t>1,725.00</t>
+        </is>
+      </c>
+      <c r="E11" s="4" t="inlineStr">
+        <is>
+          <t>38,625.00</t>
         </is>
       </c>
     </row>
@@ -2769,27 +2536,22 @@
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>2,822,471.00</t>
+          <t>13,425.00</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>3,659,691.00</t>
+          <t>20,075.00</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>1,443,598.00</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>88,925.00</t>
-        </is>
-      </c>
-      <c r="F12" s="4" t="inlineStr">
-        <is>
-          <t>8,014,685.00</t>
+          <t>4,225.00</t>
+        </is>
+      </c>
+      <c r="E12" s="4" t="inlineStr">
+        <is>
+          <t>37,725.00</t>
         </is>
       </c>
     </row>
@@ -2801,27 +2563,22 @@
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>293,200.00</t>
+          <t>500.00</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>1,134,788.00</t>
+          <t>9,325.00</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>1,552,999.00</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>48,925.00</t>
-        </is>
-      </c>
-      <c r="F13" s="4" t="inlineStr">
-        <is>
-          <t>3,029,912.00</t>
+          <t>7,925.00</t>
+        </is>
+      </c>
+      <c r="E13" s="4" t="inlineStr">
+        <is>
+          <t>17,750.00</t>
         </is>
       </c>
     </row>
@@ -2833,27 +2590,22 @@
       </c>
       <c r="B14" s="4" t="inlineStr">
         <is>
-          <t>9,809,571.00</t>
+          <t>47,150.00</t>
         </is>
       </c>
       <c r="C14" s="4" t="inlineStr">
         <is>
-          <t>7,747,774.00</t>
+          <t>33,075.00</t>
         </is>
       </c>
       <c r="D14" s="4" t="inlineStr">
         <is>
-          <t>3,670,972.00</t>
+          <t>13,875.00</t>
         </is>
       </c>
       <c r="E14" s="4" t="inlineStr">
         <is>
-          <t>247,375.00</t>
-        </is>
-      </c>
-      <c r="F14" s="4" t="inlineStr">
-        <is>
-          <t>21,475,692.00</t>
+          <t>94,100.00</t>
         </is>
       </c>
     </row>
@@ -2889,11 +2641,6 @@
       </c>
       <c r="E18" s="1" t="inlineStr">
         <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="F18" s="1" t="inlineStr">
-        <is>
           <t>Total</t>
         </is>
       </c>
@@ -2906,27 +2653,22 @@
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>2.78%</t>
+          <t>0.00%</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>6.24%</t>
+          <t>0.00%</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>8.72%</t>
-        </is>
-      </c>
-      <c r="E19" s="2" t="inlineStr">
-        <is>
           <t>0.00%</t>
         </is>
       </c>
-      <c r="F19" s="4" t="inlineStr">
-        <is>
-          <t>4.11%</t>
+      <c r="E19" s="4" t="inlineStr">
+        <is>
+          <t>0.00%</t>
         </is>
       </c>
     </row>
@@ -2938,27 +2680,22 @@
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>3.39%</t>
+          <t>0.00%</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>7.69%</t>
+          <t>14.67%</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>12.73%</t>
-        </is>
-      </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
           <t>0.00%</t>
         </is>
       </c>
-      <c r="F20" s="4" t="inlineStr">
-        <is>
-          <t>7.00%</t>
+      <c r="E20" s="4" t="inlineStr">
+        <is>
+          <t>7.81%</t>
         </is>
       </c>
     </row>
@@ -2970,27 +2707,22 @@
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>3.87%</t>
+          <t>0.00%</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>9.32%</t>
+          <t>0.00%</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>17.73%</t>
-        </is>
-      </c>
-      <c r="E21" s="2" t="inlineStr">
-        <is>
-          <t>0.00%</t>
-        </is>
-      </c>
-      <c r="F21" s="4" t="inlineStr">
-        <is>
-          <t>12.95%</t>
+          <t>18.87%</t>
+        </is>
+      </c>
+      <c r="E21" s="4" t="inlineStr">
+        <is>
+          <t>8.43%</t>
         </is>
       </c>
     </row>
@@ -3002,27 +2734,22 @@
       </c>
       <c r="B22" s="4" t="inlineStr">
         <is>
-          <t>2.99%</t>
+          <t>0.00%</t>
         </is>
       </c>
       <c r="C22" s="4" t="inlineStr">
         <is>
-          <t>7.38%</t>
+          <t>8.90%</t>
         </is>
       </c>
       <c r="D22" s="4" t="inlineStr">
         <is>
-          <t>14.11%</t>
+          <t>10.78%</t>
         </is>
       </c>
       <c r="E22" s="4" t="inlineStr">
         <is>
-          <t>0.00%</t>
-        </is>
-      </c>
-      <c r="F22" s="4" t="inlineStr">
-        <is>
-          <t>6.44%</t>
+          <t>4.72%</t>
         </is>
       </c>
     </row>
@@ -3058,11 +2785,6 @@
       </c>
       <c r="E26" s="1" t="inlineStr">
         <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="F26" s="1" t="inlineStr">
-        <is>
           <t>Total</t>
         </is>
       </c>
@@ -3075,27 +2797,22 @@
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>275,016.18</t>
+          <t>1,068.43</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>263,091.98</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>75,555.34</t>
-        </is>
-      </c>
-      <c r="E27" s="2" t="inlineStr">
-        <is>
           <t>0.00</t>
         </is>
       </c>
-      <c r="F27" s="4" t="inlineStr">
-        <is>
-          <t>613,663.50</t>
+      <c r="E27" s="4" t="inlineStr">
+        <is>
+          <t>1,068.43</t>
         </is>
       </c>
     </row>
@@ -3107,27 +2824,22 @@
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>159,584.34</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>356,612.67</t>
+          <t>2,647.62</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>225,991.67</t>
-        </is>
-      </c>
-      <c r="E28" s="2" t="inlineStr">
-        <is>
-          <t>2,158.73</t>
-        </is>
-      </c>
-      <c r="F28" s="4" t="inlineStr">
-        <is>
-          <t>744,347.41</t>
+          <t>352.94</t>
+        </is>
+      </c>
+      <c r="E28" s="4" t="inlineStr">
+        <is>
+          <t>3,000.56</t>
         </is>
       </c>
     </row>
@@ -3139,27 +2851,22 @@
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>20,644.24</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>144,899.84</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>337,727.28</t>
-        </is>
-      </c>
-      <c r="E29" s="2" t="inlineStr">
-        <is>
-          <t>5,708.02</t>
-        </is>
-      </c>
-      <c r="F29" s="4" t="inlineStr">
-        <is>
-          <t>508,979.38</t>
+          <t>2,122.93</t>
+        </is>
+      </c>
+      <c r="E29" s="4" t="inlineStr">
+        <is>
+          <t>2,122.93</t>
         </is>
       </c>
     </row>
@@ -3171,27 +2878,22 @@
       </c>
       <c r="B30" s="4" t="inlineStr">
         <is>
-          <t>455,244.76</t>
+          <t>1,068.43</t>
         </is>
       </c>
       <c r="C30" s="4" t="inlineStr">
         <is>
-          <t>764,604.49</t>
+          <t>2,647.62</t>
         </is>
       </c>
       <c r="D30" s="4" t="inlineStr">
         <is>
-          <t>639,274.29</t>
+          <t>2,475.87</t>
         </is>
       </c>
       <c r="E30" s="4" t="inlineStr">
         <is>
-          <t>7,866.75</t>
-        </is>
-      </c>
-      <c r="F30" s="4" t="inlineStr">
-        <is>
-          <t>1,866,990.29</t>
+          <t>6,191.92</t>
         </is>
       </c>
     </row>
@@ -3227,11 +2929,6 @@
       </c>
       <c r="E34" s="1" t="inlineStr">
         <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="F34" s="1" t="inlineStr">
-        <is>
           <t>Total</t>
         </is>
       </c>
@@ -3244,27 +2941,22 @@
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>6,693,900.00</t>
+          <t>33,225.00</t>
         </is>
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>2,953,295.00</t>
+          <t>3,675.00</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>674,375.00</t>
-        </is>
-      </c>
-      <c r="E35" s="2" t="inlineStr">
-        <is>
-          <t>109,525.00</t>
-        </is>
-      </c>
-      <c r="F35" s="4" t="inlineStr">
-        <is>
-          <t>10,431,095.00</t>
+          <t>1,725.00</t>
+        </is>
+      </c>
+      <c r="E35" s="4" t="inlineStr">
+        <is>
+          <t>38,625.00</t>
         </is>
       </c>
     </row>
@@ -3276,27 +2968,22 @@
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>2,822,471.00</t>
+          <t>13,425.00</t>
         </is>
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>3,659,691.00</t>
+          <t>20,075.00</t>
         </is>
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>1,443,598.00</t>
-        </is>
-      </c>
-      <c r="E36" s="2" t="inlineStr">
-        <is>
-          <t>88,925.00</t>
-        </is>
-      </c>
-      <c r="F36" s="4" t="inlineStr">
-        <is>
-          <t>8,014,685.00</t>
+          <t>4,225.00</t>
+        </is>
+      </c>
+      <c r="E36" s="4" t="inlineStr">
+        <is>
+          <t>37,725.00</t>
         </is>
       </c>
     </row>
@@ -3308,27 +2995,22 @@
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>293,200.00</t>
+          <t>500.00</t>
         </is>
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>1,134,788.00</t>
+          <t>9,325.00</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>1,552,999.00</t>
-        </is>
-      </c>
-      <c r="E37" s="2" t="inlineStr">
-        <is>
-          <t>48,925.00</t>
-        </is>
-      </c>
-      <c r="F37" s="4" t="inlineStr">
-        <is>
-          <t>3,029,912.00</t>
+          <t>7,925.00</t>
+        </is>
+      </c>
+      <c r="E37" s="4" t="inlineStr">
+        <is>
+          <t>17,750.00</t>
         </is>
       </c>
     </row>
@@ -3340,27 +3022,22 @@
       </c>
       <c r="B38" s="4" t="inlineStr">
         <is>
-          <t>9,809,571.00</t>
+          <t>47,150.00</t>
         </is>
       </c>
       <c r="C38" s="4" t="inlineStr">
         <is>
-          <t>7,747,774.00</t>
+          <t>33,075.00</t>
         </is>
       </c>
       <c r="D38" s="4" t="inlineStr">
         <is>
-          <t>3,670,972.00</t>
+          <t>13,875.00</t>
         </is>
       </c>
       <c r="E38" s="4" t="inlineStr">
         <is>
-          <t>247,375.00</t>
-        </is>
-      </c>
-      <c r="F38" s="4" t="inlineStr">
-        <is>
-          <t>21,475,692.00</t>
+          <t>94,100.00</t>
         </is>
       </c>
     </row>
@@ -3396,11 +3073,6 @@
       </c>
       <c r="E42" s="1" t="inlineStr">
         <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="F42" s="1" t="inlineStr">
-        <is>
           <t>Total</t>
         </is>
       </c>
@@ -3413,27 +3085,22 @@
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>4.11%</t>
+          <t>3.22%</t>
         </is>
       </c>
       <c r="C43" s="2" t="inlineStr">
         <is>
-          <t>8.91%</t>
+          <t>0.00%</t>
         </is>
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
-          <t>11.20%</t>
-        </is>
-      </c>
-      <c r="E43" s="2" t="inlineStr">
-        <is>
           <t>0.00%</t>
         </is>
       </c>
-      <c r="F43" s="4" t="inlineStr">
-        <is>
-          <t>5.88%</t>
+      <c r="E43" s="4" t="inlineStr">
+        <is>
+          <t>2.77%</t>
         </is>
       </c>
     </row>
@@ -3445,27 +3112,22 @@
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>5.65%</t>
+          <t>0.00%</t>
         </is>
       </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t>9.74%</t>
+          <t>13.19%</t>
         </is>
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
-          <t>15.65%</t>
-        </is>
-      </c>
-      <c r="E44" s="2" t="inlineStr">
-        <is>
-          <t>2.43%</t>
-        </is>
-      </c>
-      <c r="F44" s="4" t="inlineStr">
-        <is>
-          <t>9.29%</t>
+          <t>8.35%</t>
+        </is>
+      </c>
+      <c r="E44" s="4" t="inlineStr">
+        <is>
+          <t>7.95%</t>
         </is>
       </c>
     </row>
@@ -3477,27 +3139,22 @@
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>7.04%</t>
+          <t>0.00%</t>
         </is>
       </c>
       <c r="C45" s="2" t="inlineStr">
         <is>
-          <t>12.77%</t>
+          <t>0.00%</t>
         </is>
       </c>
       <c r="D45" s="2" t="inlineStr">
         <is>
-          <t>21.75%</t>
-        </is>
-      </c>
-      <c r="E45" s="2" t="inlineStr">
-        <is>
-          <t>11.67%</t>
-        </is>
-      </c>
-      <c r="F45" s="4" t="inlineStr">
-        <is>
-          <t>16.80%</t>
+          <t>26.79%</t>
+        </is>
+      </c>
+      <c r="E45" s="4" t="inlineStr">
+        <is>
+          <t>11.96%</t>
         </is>
       </c>
     </row>
@@ -3509,27 +3166,22 @@
       </c>
       <c r="B46" s="4" t="inlineStr">
         <is>
-          <t>4.64%</t>
+          <t>2.27%</t>
         </is>
       </c>
       <c r="C46" s="4" t="inlineStr">
         <is>
-          <t>9.87%</t>
+          <t>8.00%</t>
         </is>
       </c>
       <c r="D46" s="4" t="inlineStr">
         <is>
-          <t>17.41%</t>
+          <t>17.84%</t>
         </is>
       </c>
       <c r="E46" s="4" t="inlineStr">
         <is>
-          <t>3.18%</t>
-        </is>
-      </c>
-      <c r="F46" s="4" t="inlineStr">
-        <is>
-          <t>8.69%</t>
+          <t>6.58%</t>
         </is>
       </c>
     </row>
@@ -3544,7 +3196,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F46"/>
+  <dimension ref="A1:E46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="27" customWidth="1" min="1" max="1"/>
@@ -3552,7 +3204,6 @@
     <col width="10" customWidth="1" min="3" max="3"/>
     <col width="10" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
-    <col width="10" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -3585,11 +3236,6 @@
       </c>
       <c r="E2" s="1" t="inlineStr">
         <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="F2" s="1" t="inlineStr">
-        <is>
           <t>Total</t>
         </is>
       </c>
@@ -3602,27 +3248,22 @@
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>0.0516</t>
+          <t>0.0615</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>0.0477</t>
+          <t>0.0592</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>0.0454</t>
-        </is>
-      </c>
-      <c r="E3" s="2" t="inlineStr">
-        <is>
-          <t>0.0534</t>
-        </is>
-      </c>
-      <c r="F3" s="4" t="inlineStr">
-        <is>
-          <t>0.0500</t>
+          <t>0.0883</t>
+        </is>
+      </c>
+      <c r="E3" s="4" t="inlineStr">
+        <is>
+          <t>0.0620</t>
         </is>
       </c>
     </row>
@@ -3634,27 +3275,22 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>0.0492</t>
+          <t>0.0616</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>0.0439</t>
+          <t>0.0608</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>0.0427</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>0.0483</t>
-        </is>
-      </c>
-      <c r="F4" s="4" t="inlineStr">
-        <is>
-          <t>0.0456</t>
+          <t>0.0485</t>
+        </is>
+      </c>
+      <c r="E4" s="4" t="inlineStr">
+        <is>
+          <t>0.0592</t>
         </is>
       </c>
     </row>
@@ -3666,27 +3302,22 @@
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>0.0429</t>
+          <t>0.0304</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0.0400</t>
+          <t>0.0577</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0.0374</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>0.0397</t>
-        </is>
-      </c>
-      <c r="F5" s="4" t="inlineStr">
-        <is>
-          <t>0.0392</t>
+          <t>0.0584</t>
+        </is>
+      </c>
+      <c r="E5" s="4" t="inlineStr">
+        <is>
+          <t>0.0568</t>
         </is>
       </c>
     </row>
@@ -3698,27 +3329,22 @@
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>0.0503</t>
+          <t>0.0609</t>
         </is>
       </c>
       <c r="C6" s="4" t="inlineStr">
         <is>
-          <t>0.0442</t>
+          <t>0.0596</t>
         </is>
       </c>
       <c r="D6" s="4" t="inlineStr">
         <is>
-          <t>0.0404</t>
+          <t>0.0567</t>
         </is>
       </c>
       <c r="E6" s="4" t="inlineStr">
         <is>
-          <t>0.0476</t>
-        </is>
-      </c>
-      <c r="F6" s="4" t="inlineStr">
-        <is>
-          <t>0.0460</t>
+          <t>0.0597</t>
         </is>
       </c>
     </row>
@@ -3754,11 +3380,6 @@
       </c>
       <c r="E10" s="1" t="inlineStr">
         <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="F10" s="1" t="inlineStr">
-        <is>
           <t>Total</t>
         </is>
       </c>
@@ -3771,27 +3392,22 @@
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>2,433.24</t>
+          <t>2,274.19</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>2,514.98</t>
+          <t>3,750.00</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>2,572.24</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>2,491.18</t>
-        </is>
-      </c>
-      <c r="F11" s="4" t="inlineStr">
-        <is>
-          <t>2,466.80</t>
+          <t>2,800.00</t>
+        </is>
+      </c>
+      <c r="E11" s="4" t="inlineStr">
+        <is>
+          <t>2,452.78</t>
         </is>
       </c>
     </row>
@@ -3803,27 +3419,22 @@
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>2,054.09</t>
+          <t>1,958.33</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>2,026.09</t>
+          <t>2,603.95</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>2,080.95</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>2,315.00</t>
-        </is>
-      </c>
-      <c r="F12" s="4" t="inlineStr">
-        <is>
-          <t>2,047.33</t>
+          <t>1,433.33</t>
+        </is>
+      </c>
+      <c r="E12" s="4" t="inlineStr">
+        <is>
+          <t>2,186.25</t>
         </is>
       </c>
     </row>
@@ -3835,27 +3446,22 @@
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>1,615.89</t>
+          <t>2,050.00</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>1,729.81</t>
+          <t>2,290.91</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>1,854.63</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>1,542.14</t>
-        </is>
-      </c>
-      <c r="F13" s="4" t="inlineStr">
-        <is>
-          <t>1,770.63</t>
+          <t>1,586.36</t>
+        </is>
+      </c>
+      <c r="E13" s="4" t="inlineStr">
+        <is>
+          <t>1,943.48</t>
         </is>
       </c>
     </row>
@@ -3867,27 +3473,22 @@
       </c>
       <c r="B14" s="4" t="inlineStr">
         <is>
-          <t>2,258.31</t>
+          <t>2,168.62</t>
         </is>
       </c>
       <c r="C14" s="4" t="inlineStr">
         <is>
-          <t>2,105.13</t>
+          <t>2,637.50</t>
         </is>
       </c>
       <c r="D14" s="4" t="inlineStr">
         <is>
-          <t>2,028.90</t>
+          <t>1,602.78</t>
         </is>
       </c>
       <c r="E14" s="4" t="inlineStr">
         <is>
-          <t>2,161.57</t>
-        </is>
-      </c>
-      <c r="F14" s="4" t="inlineStr">
-        <is>
-          <t>2,154.32</t>
+          <t>2,226.77</t>
         </is>
       </c>
     </row>
@@ -3923,11 +3524,6 @@
       </c>
       <c r="E18" s="1" t="inlineStr">
         <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="F18" s="1" t="inlineStr">
-        <is>
           <t>Total</t>
         </is>
       </c>
@@ -3940,27 +3536,22 @@
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>1,468.11</t>
+          <t>1,265.32</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>1,237.69</t>
+          <t>918.75</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>1,338.05</t>
-        </is>
-      </c>
-      <c r="E19" s="2" t="inlineStr">
-        <is>
-          <t>1,555.59</t>
-        </is>
-      </c>
-      <c r="F19" s="4" t="inlineStr">
-        <is>
-          <t>1,391.06</t>
+          <t>1,725.00</t>
+        </is>
+      </c>
+      <c r="E19" s="4" t="inlineStr">
+        <is>
+          <t>1,239.58</t>
         </is>
       </c>
     </row>
@@ -3972,27 +3563,22 @@
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>1,126.33</t>
+          <t>895.00</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>924.72</t>
+          <t>1,056.58</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>980.71</t>
-        </is>
-      </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>1,257.50</t>
-        </is>
-      </c>
-      <c r="F20" s="4" t="inlineStr">
-        <is>
-          <t>1,005.83</t>
+          <t>704.17</t>
+        </is>
+      </c>
+      <c r="E20" s="4" t="inlineStr">
+        <is>
+          <t>943.12</t>
         </is>
       </c>
     </row>
@@ -4004,27 +3590,22 @@
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>820.68</t>
+          <t>500.00</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>722.56</t>
+          <t>847.73</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>772.25</t>
-        </is>
-      </c>
-      <c r="E21" s="2" t="inlineStr">
-        <is>
-          <t>853.93</t>
-        </is>
-      </c>
-      <c r="F21" s="4" t="inlineStr">
-        <is>
-          <t>757.16</t>
+          <t>720.45</t>
+        </is>
+      </c>
+      <c r="E21" s="4" t="inlineStr">
+        <is>
+          <t>771.74</t>
         </is>
       </c>
     </row>
@@ -4036,27 +3617,22 @@
       </c>
       <c r="B22" s="4" t="inlineStr">
         <is>
-          <t>1,315.06</t>
+          <t>1,130.85</t>
         </is>
       </c>
       <c r="C22" s="4" t="inlineStr">
         <is>
-          <t>972.69</t>
+          <t>972.79</t>
         </is>
       </c>
       <c r="D22" s="4" t="inlineStr">
         <is>
-          <t>920.74</t>
+          <t>770.83</t>
         </is>
       </c>
       <c r="E22" s="4" t="inlineStr">
         <is>
-          <t>1,246.08</t>
-        </is>
-      </c>
-      <c r="F22" s="4" t="inlineStr">
-        <is>
-          <t>1,105.17</t>
+          <t>1,011.11</t>
         </is>
       </c>
     </row>
@@ -4092,11 +3668,6 @@
       </c>
       <c r="E26" s="1" t="inlineStr">
         <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="F26" s="1" t="inlineStr">
-        <is>
           <t>Total</t>
         </is>
       </c>
@@ -4109,27 +3680,22 @@
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>1,931.06</t>
+          <t>2,065.67</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>2,554.61</t>
+          <t>1,797.82</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>3,525.18</t>
-        </is>
-      </c>
-      <c r="E27" s="2" t="inlineStr">
-        <is>
-          <t>3,240.89</t>
-        </is>
-      </c>
-      <c r="F27" s="4" t="inlineStr">
-        <is>
-          <t>2,226.25</t>
+          <t>6,621.90</t>
+        </is>
+      </c>
+      <c r="E27" s="4" t="inlineStr">
+        <is>
+          <t>2,162.47</t>
         </is>
       </c>
     </row>
@@ -4141,27 +3707,22 @@
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>1,317.57</t>
+          <t>1,231.29</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>1,634.29</t>
+          <t>2,178.84</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>2,092.10</t>
-        </is>
-      </c>
-      <c r="E28" s="2" t="inlineStr">
-        <is>
-          <t>1,554.62</t>
-        </is>
-      </c>
-      <c r="F28" s="4" t="inlineStr">
-        <is>
-          <t>1,597.24</t>
+          <t>1,710.21</t>
+        </is>
+      </c>
+      <c r="E28" s="4" t="inlineStr">
+        <is>
+          <t>1,753.21</t>
         </is>
       </c>
     </row>
@@ -4173,27 +3734,22 @@
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>1,025.55</t>
+          <t>1,990.17</t>
         </is>
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>1,298.54</t>
+          <t>2,203.68</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>1,611.86</t>
-        </is>
-      </c>
-      <c r="E29" s="2" t="inlineStr">
-        <is>
-          <t>1,404.16</t>
-        </is>
-      </c>
-      <c r="F29" s="4" t="inlineStr">
-        <is>
-          <t>1,411.36</t>
+          <t>1,592.92</t>
+        </is>
+      </c>
+      <c r="E29" s="4" t="inlineStr">
+        <is>
+          <t>1,902.29</t>
         </is>
       </c>
     </row>
@@ -4205,27 +3761,22 @@
       </c>
       <c r="B30" s="4" t="inlineStr">
         <is>
-          <t>1,669.64</t>
+          <t>1,797.78</t>
         </is>
       </c>
       <c r="C30" s="4" t="inlineStr">
         <is>
-          <t>1,829.89</t>
+          <t>2,142.05</t>
         </is>
       </c>
       <c r="D30" s="4" t="inlineStr">
         <is>
-          <t>2,031.03</t>
+          <t>1,911.41</t>
         </is>
       </c>
       <c r="E30" s="4" t="inlineStr">
         <is>
-          <t>2,075.41</t>
-        </is>
-      </c>
-      <c r="F30" s="4" t="inlineStr">
-        <is>
-          <t>1,803.25</t>
+          <t>1,936.67</t>
         </is>
       </c>
     </row>
@@ -4261,11 +3812,6 @@
       </c>
       <c r="E34" s="1" t="inlineStr">
         <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="F34" s="1" t="inlineStr">
-        <is>
           <t>Total</t>
         </is>
       </c>
@@ -4278,27 +3824,22 @@
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>1,542.28</t>
+          <t>1,627.83</t>
         </is>
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>2,191.62</t>
+          <t>1,456.17</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>3,135.60</t>
-        </is>
-      </c>
-      <c r="E35" s="2" t="inlineStr">
-        <is>
-          <t>2,844.13</t>
-        </is>
-      </c>
-      <c r="F35" s="4" t="inlineStr">
-        <is>
-          <t>1,845.23</t>
+          <t>5,839.90</t>
+        </is>
+      </c>
+      <c r="E35" s="4" t="inlineStr">
+        <is>
+          <t>1,725.76</t>
         </is>
       </c>
     </row>
@@ -4310,27 +3851,22 @@
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>1,041.78</t>
+          <t>905.49</t>
         </is>
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>1,385.62</t>
+          <t>1,809.44</t>
         </is>
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>1,829.73</t>
-        </is>
-      </c>
-      <c r="E36" s="2" t="inlineStr">
-        <is>
-          <t>1,275.10</t>
-        </is>
-      </c>
-      <c r="F36" s="4" t="inlineStr">
-        <is>
-          <t>1,336.84</t>
+          <t>1,415.17</t>
+        </is>
+      </c>
+      <c r="E36" s="4" t="inlineStr">
+        <is>
+          <t>1,411.32</t>
         </is>
       </c>
     </row>
@@ -4342,27 +3878,22 @@
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>825.86</t>
+          <t>1,712.84</t>
         </is>
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>1,110.42</t>
+          <t>1,904.64</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>1,418.84</t>
-        </is>
-      </c>
-      <c r="E37" s="2" t="inlineStr">
-        <is>
-          <t>1,215.35</t>
-        </is>
-      </c>
-      <c r="F37" s="4" t="inlineStr">
-        <is>
-          <t>1,219.82</t>
+          <t>1,322.81</t>
+        </is>
+      </c>
+      <c r="E37" s="4" t="inlineStr">
+        <is>
+          <t>1,618.03</t>
         </is>
       </c>
     </row>
@@ -4374,27 +3905,22 @@
       </c>
       <c r="B38" s="4" t="inlineStr">
         <is>
-          <t>1,330.17</t>
+          <t>1,399.10</t>
         </is>
       </c>
       <c r="C38" s="4" t="inlineStr">
         <is>
-          <t>1,560.90</t>
+          <t>1,798.68</t>
         </is>
       </c>
       <c r="D38" s="4" t="inlineStr">
         <is>
-          <t>1,787.56</t>
+          <t>1,604.54</t>
         </is>
       </c>
       <c r="E38" s="4" t="inlineStr">
         <is>
-          <t>1,781.71</t>
-        </is>
-      </c>
-      <c r="F38" s="4" t="inlineStr">
-        <is>
-          <t>1,509.96</t>
+          <t>1,573.68</t>
         </is>
       </c>
     </row>
@@ -4430,11 +3956,6 @@
       </c>
       <c r="E42" s="1" t="inlineStr">
         <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="F42" s="1" t="inlineStr">
-        <is>
           <t>Total</t>
         </is>
       </c>
@@ -4447,27 +3968,22 @@
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>8,034.17</t>
+          <t>7,457.20</t>
         </is>
       </c>
       <c r="C43" s="2" t="inlineStr">
         <is>
-          <t>8,221.79</t>
+          <t>5,954.48</t>
         </is>
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
-          <t>9,406.98</t>
-        </is>
-      </c>
-      <c r="E43" s="2" t="inlineStr">
-        <is>
-          <t>8,982.37</t>
-        </is>
-      </c>
-      <c r="F43" s="4" t="inlineStr">
-        <is>
-          <t>8,179.89</t>
+          <t>8,855.95</t>
+        </is>
+      </c>
+      <c r="E43" s="4" t="inlineStr">
+        <is>
+          <t>7,329.09</t>
         </is>
       </c>
     </row>
@@ -4479,27 +3995,22 @@
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>5,949.09</t>
+          <t>5,538.86</t>
         </is>
       </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t>6,057.57</t>
+          <t>6,692.27</t>
         </is>
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
-          <t>6,600.02</t>
-        </is>
-      </c>
-      <c r="E44" s="2" t="inlineStr">
-        <is>
-          <t>6,035.73</t>
-        </is>
-      </c>
-      <c r="F44" s="4" t="inlineStr">
-        <is>
-          <t>6,105.45</t>
+          <t>6,239.74</t>
+        </is>
+      </c>
+      <c r="E44" s="4" t="inlineStr">
+        <is>
+          <t>6,191.86</t>
         </is>
       </c>
     </row>
@@ -4511,27 +4022,22 @@
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>4,941.93</t>
+          <t>9,123.40</t>
         </is>
       </c>
       <c r="C45" s="2" t="inlineStr">
         <is>
-          <t>4,995.38</t>
+          <t>5,929.26</t>
         </is>
       </c>
       <c r="D45" s="2" t="inlineStr">
         <is>
-          <t>5,474.73</t>
-        </is>
-      </c>
-      <c r="E45" s="2" t="inlineStr">
-        <is>
-          <t>5,079.90</t>
-        </is>
-      </c>
-      <c r="F45" s="4" t="inlineStr">
-        <is>
-          <t>5,205.22</t>
+          <t>5,040.43</t>
+        </is>
+      </c>
+      <c r="E45" s="4" t="inlineStr">
+        <is>
+          <t>5,643.04</t>
         </is>
       </c>
     </row>
@@ -4543,27 +4049,22 @@
       </c>
       <c r="B46" s="4" t="inlineStr">
         <is>
-          <t>7,144.92</t>
+          <t>6,880.42</t>
         </is>
       </c>
       <c r="C46" s="4" t="inlineStr">
         <is>
-          <t>6,460.06</t>
+          <t>6,358.62</t>
         </is>
       </c>
       <c r="D46" s="4" t="inlineStr">
         <is>
-          <t>6,387.27</t>
+          <t>5,652.17</t>
         </is>
       </c>
       <c r="E46" s="4" t="inlineStr">
         <is>
-          <t>6,755.56</t>
-        </is>
-      </c>
-      <c r="F46" s="4" t="inlineStr">
-        <is>
-          <t>6,727.73</t>
+          <t>6,477.90</t>
         </is>
       </c>
     </row>
@@ -4578,7 +4079,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F102"/>
+  <dimension ref="A1:E102"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="32" customWidth="1" min="1" max="1"/>
@@ -4586,7 +4087,6 @@
     <col width="10" customWidth="1" min="3" max="3"/>
     <col width="10" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
-    <col width="10" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -4619,11 +4119,6 @@
       </c>
       <c r="E2" s="1" t="inlineStr">
         <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="F2" s="1" t="inlineStr">
-        <is>
           <t>Total</t>
         </is>
       </c>
@@ -4636,27 +4131,22 @@
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>5,480</t>
+          <t>31</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>2,670</t>
+          <t>4</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>504</t>
-        </is>
-      </c>
-      <c r="E3" s="2" t="inlineStr">
-        <is>
-          <t>85</t>
-        </is>
-      </c>
-      <c r="F3" s="4" t="inlineStr">
-        <is>
-          <t>8,739</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E3" s="4" t="inlineStr">
+        <is>
+          <t>36</t>
         </is>
       </c>
     </row>
@@ -4668,27 +4158,22 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>3,200</t>
+          <t>15</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>4,609</t>
+          <t>19</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>1,472</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="F4" s="4" t="inlineStr">
-        <is>
-          <t>9,381</t>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="E4" s="4" t="inlineStr">
+        <is>
+          <t>40</t>
         </is>
       </c>
     </row>
@@ -4700,27 +4185,22 @@
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>475</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>1,945</t>
+          <t>11</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>2,011</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>70</t>
-        </is>
-      </c>
-      <c r="F5" s="4" t="inlineStr">
-        <is>
-          <t>4,501</t>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="E5" s="4" t="inlineStr">
+        <is>
+          <t>23</t>
         </is>
       </c>
     </row>
@@ -4732,27 +4212,22 @@
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>9,155</t>
+          <t>47</t>
         </is>
       </c>
       <c r="C6" s="4" t="inlineStr">
         <is>
-          <t>9,224</t>
+          <t>34</t>
         </is>
       </c>
       <c r="D6" s="4" t="inlineStr">
         <is>
-          <t>3,987</t>
+          <t>18</t>
         </is>
       </c>
       <c r="E6" s="4" t="inlineStr">
         <is>
-          <t>255</t>
-        </is>
-      </c>
-      <c r="F6" s="4" t="inlineStr">
-        <is>
-          <t>22,621</t>
+          <t>99</t>
         </is>
       </c>
     </row>
@@ -4788,11 +4263,6 @@
       </c>
       <c r="E10" s="1" t="inlineStr">
         <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="F10" s="1" t="inlineStr">
-        <is>
           <t>Total</t>
         </is>
       </c>
@@ -4805,27 +4275,22 @@
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>5,480</t>
+          <t>31</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>2,670</t>
+          <t>4</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>504</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>85</t>
-        </is>
-      </c>
-      <c r="F11" s="4" t="inlineStr">
-        <is>
-          <t>8,739</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E11" s="4" t="inlineStr">
+        <is>
+          <t>36</t>
         </is>
       </c>
     </row>
@@ -4837,27 +4302,22 @@
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>3,200</t>
+          <t>15</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>4,609</t>
+          <t>19</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>1,472</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="F12" s="4" t="inlineStr">
-        <is>
-          <t>9,381</t>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="E12" s="4" t="inlineStr">
+        <is>
+          <t>40</t>
         </is>
       </c>
     </row>
@@ -4869,27 +4329,22 @@
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>475</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>1,945</t>
+          <t>11</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>2,011</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>70</t>
-        </is>
-      </c>
-      <c r="F13" s="4" t="inlineStr">
-        <is>
-          <t>4,501</t>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="E13" s="4" t="inlineStr">
+        <is>
+          <t>23</t>
         </is>
       </c>
     </row>
@@ -4901,27 +4356,22 @@
       </c>
       <c r="B14" s="4" t="inlineStr">
         <is>
-          <t>9,155</t>
+          <t>47</t>
         </is>
       </c>
       <c r="C14" s="4" t="inlineStr">
         <is>
-          <t>9,224</t>
+          <t>34</t>
         </is>
       </c>
       <c r="D14" s="4" t="inlineStr">
         <is>
-          <t>3,987</t>
+          <t>18</t>
         </is>
       </c>
       <c r="E14" s="4" t="inlineStr">
         <is>
-          <t>255</t>
-        </is>
-      </c>
-      <c r="F14" s="4" t="inlineStr">
-        <is>
-          <t>22,621</t>
+          <t>99</t>
         </is>
       </c>
     </row>
@@ -4957,11 +4407,6 @@
       </c>
       <c r="E18" s="1" t="inlineStr">
         <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="F18" s="1" t="inlineStr">
-        <is>
           <t>Total</t>
         </is>
       </c>
@@ -4974,27 +4419,22 @@
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>5,480</t>
+          <t>31</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>2,670</t>
+          <t>4</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>504</t>
-        </is>
-      </c>
-      <c r="E19" s="2" t="inlineStr">
-        <is>
-          <t>85</t>
-        </is>
-      </c>
-      <c r="F19" s="4" t="inlineStr">
-        <is>
-          <t>8,739</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E19" s="4" t="inlineStr">
+        <is>
+          <t>36</t>
         </is>
       </c>
     </row>
@@ -5006,27 +4446,22 @@
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>3,200</t>
+          <t>15</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>4,609</t>
+          <t>19</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>1,472</t>
-        </is>
-      </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="F20" s="4" t="inlineStr">
-        <is>
-          <t>9,381</t>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="E20" s="4" t="inlineStr">
+        <is>
+          <t>40</t>
         </is>
       </c>
     </row>
@@ -5038,27 +4473,22 @@
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>475</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>1,945</t>
+          <t>11</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>2,011</t>
-        </is>
-      </c>
-      <c r="E21" s="2" t="inlineStr">
-        <is>
-          <t>70</t>
-        </is>
-      </c>
-      <c r="F21" s="4" t="inlineStr">
-        <is>
-          <t>4,501</t>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="E21" s="4" t="inlineStr">
+        <is>
+          <t>23</t>
         </is>
       </c>
     </row>
@@ -5070,27 +4500,22 @@
       </c>
       <c r="B22" s="4" t="inlineStr">
         <is>
-          <t>9,155</t>
+          <t>47</t>
         </is>
       </c>
       <c r="C22" s="4" t="inlineStr">
         <is>
-          <t>9,224</t>
+          <t>34</t>
         </is>
       </c>
       <c r="D22" s="4" t="inlineStr">
         <is>
-          <t>3,987</t>
+          <t>18</t>
         </is>
       </c>
       <c r="E22" s="4" t="inlineStr">
         <is>
-          <t>255</t>
-        </is>
-      </c>
-      <c r="F22" s="4" t="inlineStr">
-        <is>
-          <t>22,621</t>
+          <t>99</t>
         </is>
       </c>
     </row>
@@ -5126,11 +4551,6 @@
       </c>
       <c r="E26" s="1" t="inlineStr">
         <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="F26" s="1" t="inlineStr">
-        <is>
           <t>Total</t>
         </is>
       </c>
@@ -5143,27 +4563,22 @@
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>1,721</t>
+          <t>12</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>889</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>134</t>
-        </is>
-      </c>
-      <c r="E27" s="2" t="inlineStr">
-        <is>
-          <t>21</t>
-        </is>
-      </c>
-      <c r="F27" s="4" t="inlineStr">
-        <is>
-          <t>2,765</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E27" s="4" t="inlineStr">
+        <is>
+          <t>15</t>
         </is>
       </c>
     </row>
@@ -5175,27 +4590,22 @@
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>931</t>
+          <t>7</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>1,510</t>
+          <t>12</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>393</t>
-        </is>
-      </c>
-      <c r="E28" s="2" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="F28" s="4" t="inlineStr">
-        <is>
-          <t>2,850</t>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E28" s="4" t="inlineStr">
+        <is>
+          <t>22</t>
         </is>
       </c>
     </row>
@@ -5207,27 +4617,22 @@
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>117</t>
+          <t>0</t>
         </is>
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>509</t>
+          <t>3</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>233</t>
-        </is>
-      </c>
-      <c r="E29" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="F29" s="4" t="inlineStr">
-        <is>
-          <t>863</t>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E29" s="4" t="inlineStr">
+        <is>
+          <t>8</t>
         </is>
       </c>
     </row>
@@ -5239,27 +4644,22 @@
       </c>
       <c r="B30" s="4" t="inlineStr">
         <is>
-          <t>2,769</t>
+          <t>19</t>
         </is>
       </c>
       <c r="C30" s="4" t="inlineStr">
         <is>
-          <t>2,908</t>
+          <t>17</t>
         </is>
       </c>
       <c r="D30" s="4" t="inlineStr">
         <is>
-          <t>760</t>
+          <t>9</t>
         </is>
       </c>
       <c r="E30" s="4" t="inlineStr">
         <is>
-          <t>41</t>
-        </is>
-      </c>
-      <c r="F30" s="4" t="inlineStr">
-        <is>
-          <t>6,478</t>
+          <t>45</t>
         </is>
       </c>
     </row>
@@ -5295,11 +4695,6 @@
       </c>
       <c r="E34" s="1" t="inlineStr">
         <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="F34" s="1" t="inlineStr">
-        <is>
           <t>Total</t>
         </is>
       </c>
@@ -5312,27 +4707,22 @@
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>3,759</t>
+          <t>19</t>
         </is>
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>1,781</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>370</t>
-        </is>
-      </c>
-      <c r="E35" s="2" t="inlineStr">
-        <is>
-          <t>64</t>
-        </is>
-      </c>
-      <c r="F35" s="4" t="inlineStr">
-        <is>
-          <t>5,974</t>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E35" s="4" t="inlineStr">
+        <is>
+          <t>21</t>
         </is>
       </c>
     </row>
@@ -5344,27 +4734,22 @@
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>2,269</t>
+          <t>8</t>
         </is>
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>3,099</t>
+          <t>7</t>
         </is>
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>1,079</t>
-        </is>
-      </c>
-      <c r="E36" s="2" t="inlineStr">
-        <is>
-          <t>84</t>
-        </is>
-      </c>
-      <c r="F36" s="4" t="inlineStr">
-        <is>
-          <t>6,531</t>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E36" s="4" t="inlineStr">
+        <is>
+          <t>18</t>
         </is>
       </c>
     </row>
@@ -5376,27 +4761,22 @@
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>358</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>1,436</t>
+          <t>8</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>1,778</t>
-        </is>
-      </c>
-      <c r="E37" s="2" t="inlineStr">
-        <is>
-          <t>66</t>
-        </is>
-      </c>
-      <c r="F37" s="4" t="inlineStr">
-        <is>
-          <t>3,638</t>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="E37" s="4" t="inlineStr">
+        <is>
+          <t>15</t>
         </is>
       </c>
     </row>
@@ -5408,27 +4788,22 @@
       </c>
       <c r="B38" s="4" t="inlineStr">
         <is>
-          <t>6,386</t>
+          <t>28</t>
         </is>
       </c>
       <c r="C38" s="4" t="inlineStr">
         <is>
-          <t>6,316</t>
+          <t>17</t>
         </is>
       </c>
       <c r="D38" s="4" t="inlineStr">
         <is>
-          <t>3,227</t>
+          <t>9</t>
         </is>
       </c>
       <c r="E38" s="4" t="inlineStr">
         <is>
-          <t>214</t>
-        </is>
-      </c>
-      <c r="F38" s="4" t="inlineStr">
-        <is>
-          <t>16,143</t>
+          <t>54</t>
         </is>
       </c>
     </row>
@@ -5464,11 +4839,6 @@
       </c>
       <c r="E42" s="1" t="inlineStr">
         <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="F42" s="1" t="inlineStr">
-        <is>
           <t>Total</t>
         </is>
       </c>
@@ -5481,27 +4851,22 @@
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>5,480</t>
+          <t>31</t>
         </is>
       </c>
       <c r="C43" s="2" t="inlineStr">
         <is>
-          <t>2,670</t>
+          <t>4</t>
         </is>
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
-          <t>504</t>
-        </is>
-      </c>
-      <c r="E43" s="2" t="inlineStr">
-        <is>
-          <t>85</t>
-        </is>
-      </c>
-      <c r="F43" s="4" t="inlineStr">
-        <is>
-          <t>8,739</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E43" s="4" t="inlineStr">
+        <is>
+          <t>36</t>
         </is>
       </c>
     </row>
@@ -5513,27 +4878,22 @@
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>3,200</t>
+          <t>15</t>
         </is>
       </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t>4,609</t>
+          <t>19</t>
         </is>
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
-          <t>1,472</t>
-        </is>
-      </c>
-      <c r="E44" s="2" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="F44" s="4" t="inlineStr">
-        <is>
-          <t>9,381</t>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="E44" s="4" t="inlineStr">
+        <is>
+          <t>40</t>
         </is>
       </c>
     </row>
@@ -5545,27 +4905,22 @@
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>475</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C45" s="2" t="inlineStr">
         <is>
-          <t>1,945</t>
+          <t>11</t>
         </is>
       </c>
       <c r="D45" s="2" t="inlineStr">
         <is>
-          <t>2,011</t>
-        </is>
-      </c>
-      <c r="E45" s="2" t="inlineStr">
-        <is>
-          <t>70</t>
-        </is>
-      </c>
-      <c r="F45" s="4" t="inlineStr">
-        <is>
-          <t>4,501</t>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="E45" s="4" t="inlineStr">
+        <is>
+          <t>23</t>
         </is>
       </c>
     </row>
@@ -5577,27 +4932,22 @@
       </c>
       <c r="B46" s="4" t="inlineStr">
         <is>
-          <t>9,155</t>
+          <t>47</t>
         </is>
       </c>
       <c r="C46" s="4" t="inlineStr">
         <is>
-          <t>9,224</t>
+          <t>34</t>
         </is>
       </c>
       <c r="D46" s="4" t="inlineStr">
         <is>
-          <t>3,987</t>
+          <t>18</t>
         </is>
       </c>
       <c r="E46" s="4" t="inlineStr">
         <is>
-          <t>255</t>
-        </is>
-      </c>
-      <c r="F46" s="4" t="inlineStr">
-        <is>
-          <t>22,621</t>
+          <t>99</t>
         </is>
       </c>
     </row>
@@ -5633,11 +4983,6 @@
       </c>
       <c r="E50" s="1" t="inlineStr">
         <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="F50" s="1" t="inlineStr">
-        <is>
           <t>Total</t>
         </is>
       </c>
@@ -5663,12 +5008,7 @@
           <t>100.00%</t>
         </is>
       </c>
-      <c r="E51" s="2" t="inlineStr">
-        <is>
-          <t>100.00%</t>
-        </is>
-      </c>
-      <c r="F51" s="4" t="inlineStr">
+      <c r="E51" s="4" t="inlineStr">
         <is>
           <t>100.00%</t>
         </is>
@@ -5695,12 +5035,7 @@
           <t>100.00%</t>
         </is>
       </c>
-      <c r="E52" s="2" t="inlineStr">
-        <is>
-          <t>100.00%</t>
-        </is>
-      </c>
-      <c r="F52" s="4" t="inlineStr">
+      <c r="E52" s="4" t="inlineStr">
         <is>
           <t>100.00%</t>
         </is>
@@ -5727,12 +5062,7 @@
           <t>100.00%</t>
         </is>
       </c>
-      <c r="E53" s="2" t="inlineStr">
-        <is>
-          <t>100.00%</t>
-        </is>
-      </c>
-      <c r="F53" s="4" t="inlineStr">
+      <c r="E53" s="4" t="inlineStr">
         <is>
           <t>100.00%</t>
         </is>
@@ -5760,11 +5090,6 @@
         </is>
       </c>
       <c r="E54" s="4" t="inlineStr">
-        <is>
-          <t>100.00%</t>
-        </is>
-      </c>
-      <c r="F54" s="4" t="inlineStr">
         <is>
           <t>100.00%</t>
         </is>
@@ -5802,11 +5127,6 @@
       </c>
       <c r="E58" s="1" t="inlineStr">
         <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="F58" s="1" t="inlineStr">
-        <is>
           <t>Total</t>
         </is>
       </c>
@@ -5832,12 +5152,7 @@
           <t>100.00%</t>
         </is>
       </c>
-      <c r="E59" s="2" t="inlineStr">
-        <is>
-          <t>100.00%</t>
-        </is>
-      </c>
-      <c r="F59" s="4" t="inlineStr">
+      <c r="E59" s="4" t="inlineStr">
         <is>
           <t>100.00%</t>
         </is>
@@ -5864,12 +5179,7 @@
           <t>100.00%</t>
         </is>
       </c>
-      <c r="E60" s="2" t="inlineStr">
-        <is>
-          <t>100.00%</t>
-        </is>
-      </c>
-      <c r="F60" s="4" t="inlineStr">
+      <c r="E60" s="4" t="inlineStr">
         <is>
           <t>100.00%</t>
         </is>
@@ -5896,12 +5206,7 @@
           <t>100.00%</t>
         </is>
       </c>
-      <c r="E61" s="2" t="inlineStr">
-        <is>
-          <t>100.00%</t>
-        </is>
-      </c>
-      <c r="F61" s="4" t="inlineStr">
+      <c r="E61" s="4" t="inlineStr">
         <is>
           <t>100.00%</t>
         </is>
@@ -5929,11 +5234,6 @@
         </is>
       </c>
       <c r="E62" s="4" t="inlineStr">
-        <is>
-          <t>100.00%</t>
-        </is>
-      </c>
-      <c r="F62" s="4" t="inlineStr">
         <is>
           <t>100.00%</t>
         </is>
@@ -5971,11 +5271,6 @@
       </c>
       <c r="E66" s="1" t="inlineStr">
         <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="F66" s="1" t="inlineStr">
-        <is>
           <t>Total</t>
         </is>
       </c>
@@ -5988,27 +5283,22 @@
       </c>
       <c r="B67" s="2" t="inlineStr">
         <is>
-          <t>31.41%</t>
+          <t>38.71%</t>
         </is>
       </c>
       <c r="C67" s="2" t="inlineStr">
         <is>
-          <t>33.30%</t>
+          <t>50.00%</t>
         </is>
       </c>
       <c r="D67" s="2" t="inlineStr">
         <is>
-          <t>26.59%</t>
-        </is>
-      </c>
-      <c r="E67" s="2" t="inlineStr">
-        <is>
-          <t>24.71%</t>
-        </is>
-      </c>
-      <c r="F67" s="4" t="inlineStr">
-        <is>
-          <t>31.64%</t>
+          <t>100.00%</t>
+        </is>
+      </c>
+      <c r="E67" s="4" t="inlineStr">
+        <is>
+          <t>41.67%</t>
         </is>
       </c>
     </row>
@@ -6020,27 +5310,22 @@
       </c>
       <c r="B68" s="2" t="inlineStr">
         <is>
-          <t>29.09%</t>
+          <t>46.67%</t>
         </is>
       </c>
       <c r="C68" s="2" t="inlineStr">
         <is>
-          <t>32.76%</t>
+          <t>63.16%</t>
         </is>
       </c>
       <c r="D68" s="2" t="inlineStr">
         <is>
-          <t>26.70%</t>
-        </is>
-      </c>
-      <c r="E68" s="2" t="inlineStr">
-        <is>
-          <t>16.00%</t>
-        </is>
-      </c>
-      <c r="F68" s="4" t="inlineStr">
-        <is>
-          <t>30.38%</t>
+          <t>50.00%</t>
+        </is>
+      </c>
+      <c r="E68" s="4" t="inlineStr">
+        <is>
+          <t>55.00%</t>
         </is>
       </c>
     </row>
@@ -6052,27 +5337,22 @@
       </c>
       <c r="B69" s="2" t="inlineStr">
         <is>
-          <t>24.63%</t>
+          <t>0.00%</t>
         </is>
       </c>
       <c r="C69" s="2" t="inlineStr">
         <is>
-          <t>26.17%</t>
+          <t>27.27%</t>
         </is>
       </c>
       <c r="D69" s="2" t="inlineStr">
         <is>
-          <t>11.59%</t>
-        </is>
-      </c>
-      <c r="E69" s="2" t="inlineStr">
-        <is>
-          <t>5.71%</t>
-        </is>
-      </c>
-      <c r="F69" s="4" t="inlineStr">
-        <is>
-          <t>19.17%</t>
+          <t>45.45%</t>
+        </is>
+      </c>
+      <c r="E69" s="4" t="inlineStr">
+        <is>
+          <t>34.78%</t>
         </is>
       </c>
     </row>
@@ -6084,27 +5364,22 @@
       </c>
       <c r="B70" s="4" t="inlineStr">
         <is>
-          <t>30.25%</t>
+          <t>40.43%</t>
         </is>
       </c>
       <c r="C70" s="4" t="inlineStr">
         <is>
-          <t>31.53%</t>
+          <t>50.00%</t>
         </is>
       </c>
       <c r="D70" s="4" t="inlineStr">
         <is>
-          <t>19.06%</t>
+          <t>50.00%</t>
         </is>
       </c>
       <c r="E70" s="4" t="inlineStr">
         <is>
-          <t>16.08%</t>
-        </is>
-      </c>
-      <c r="F70" s="4" t="inlineStr">
-        <is>
-          <t>28.64%</t>
+          <t>45.45%</t>
         </is>
       </c>
     </row>
@@ -6140,11 +5415,6 @@
       </c>
       <c r="E74" s="1" t="inlineStr">
         <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="F74" s="1" t="inlineStr">
-        <is>
           <t>Total</t>
         </is>
       </c>
@@ -6157,27 +5427,22 @@
       </c>
       <c r="B75" s="2" t="inlineStr">
         <is>
-          <t>68.59%</t>
+          <t>61.29%</t>
         </is>
       </c>
       <c r="C75" s="2" t="inlineStr">
         <is>
-          <t>66.70%</t>
+          <t>50.00%</t>
         </is>
       </c>
       <c r="D75" s="2" t="inlineStr">
         <is>
-          <t>73.41%</t>
-        </is>
-      </c>
-      <c r="E75" s="2" t="inlineStr">
-        <is>
-          <t>75.29%</t>
-        </is>
-      </c>
-      <c r="F75" s="4" t="inlineStr">
-        <is>
-          <t>68.36%</t>
+          <t>0.00%</t>
+        </is>
+      </c>
+      <c r="E75" s="4" t="inlineStr">
+        <is>
+          <t>58.33%</t>
         </is>
       </c>
     </row>
@@ -6189,27 +5454,22 @@
       </c>
       <c r="B76" s="2" t="inlineStr">
         <is>
-          <t>70.91%</t>
+          <t>53.33%</t>
         </is>
       </c>
       <c r="C76" s="2" t="inlineStr">
         <is>
-          <t>67.24%</t>
+          <t>36.84%</t>
         </is>
       </c>
       <c r="D76" s="2" t="inlineStr">
         <is>
-          <t>73.30%</t>
-        </is>
-      </c>
-      <c r="E76" s="2" t="inlineStr">
-        <is>
-          <t>84.00%</t>
-        </is>
-      </c>
-      <c r="F76" s="4" t="inlineStr">
-        <is>
-          <t>69.62%</t>
+          <t>50.00%</t>
+        </is>
+      </c>
+      <c r="E76" s="4" t="inlineStr">
+        <is>
+          <t>45.00%</t>
         </is>
       </c>
     </row>
@@ -6221,27 +5481,22 @@
       </c>
       <c r="B77" s="2" t="inlineStr">
         <is>
-          <t>75.37%</t>
+          <t>100.00%</t>
         </is>
       </c>
       <c r="C77" s="2" t="inlineStr">
         <is>
-          <t>73.83%</t>
+          <t>72.73%</t>
         </is>
       </c>
       <c r="D77" s="2" t="inlineStr">
         <is>
-          <t>88.41%</t>
-        </is>
-      </c>
-      <c r="E77" s="2" t="inlineStr">
-        <is>
-          <t>94.29%</t>
-        </is>
-      </c>
-      <c r="F77" s="4" t="inlineStr">
-        <is>
-          <t>80.83%</t>
+          <t>54.55%</t>
+        </is>
+      </c>
+      <c r="E77" s="4" t="inlineStr">
+        <is>
+          <t>65.22%</t>
         </is>
       </c>
     </row>
@@ -6253,27 +5508,22 @@
       </c>
       <c r="B78" s="4" t="inlineStr">
         <is>
-          <t>69.75%</t>
+          <t>59.57%</t>
         </is>
       </c>
       <c r="C78" s="4" t="inlineStr">
         <is>
-          <t>68.47%</t>
+          <t>50.00%</t>
         </is>
       </c>
       <c r="D78" s="4" t="inlineStr">
         <is>
-          <t>80.94%</t>
+          <t>50.00%</t>
         </is>
       </c>
       <c r="E78" s="4" t="inlineStr">
         <is>
-          <t>83.92%</t>
-        </is>
-      </c>
-      <c r="F78" s="4" t="inlineStr">
-        <is>
-          <t>71.36%</t>
+          <t>54.55%</t>
         </is>
       </c>
     </row>
@@ -6309,11 +5559,6 @@
       </c>
       <c r="E82" s="1" t="inlineStr">
         <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="F82" s="1" t="inlineStr">
-        <is>
           <t>Total</t>
         </is>
       </c>
@@ -6326,27 +5571,22 @@
       </c>
       <c r="B83" s="2" t="inlineStr">
         <is>
-          <t>31.41%</t>
+          <t>38.71%</t>
         </is>
       </c>
       <c r="C83" s="2" t="inlineStr">
         <is>
-          <t>33.30%</t>
+          <t>50.00%</t>
         </is>
       </c>
       <c r="D83" s="2" t="inlineStr">
         <is>
-          <t>26.59%</t>
-        </is>
-      </c>
-      <c r="E83" s="2" t="inlineStr">
-        <is>
-          <t>24.71%</t>
-        </is>
-      </c>
-      <c r="F83" s="4" t="inlineStr">
-        <is>
-          <t>31.64%</t>
+          <t>100.00%</t>
+        </is>
+      </c>
+      <c r="E83" s="4" t="inlineStr">
+        <is>
+          <t>41.67%</t>
         </is>
       </c>
     </row>
@@ -6358,27 +5598,22 @@
       </c>
       <c r="B84" s="2" t="inlineStr">
         <is>
-          <t>29.09%</t>
+          <t>46.67%</t>
         </is>
       </c>
       <c r="C84" s="2" t="inlineStr">
         <is>
-          <t>32.76%</t>
+          <t>63.16%</t>
         </is>
       </c>
       <c r="D84" s="2" t="inlineStr">
         <is>
-          <t>26.70%</t>
-        </is>
-      </c>
-      <c r="E84" s="2" t="inlineStr">
-        <is>
-          <t>16.00%</t>
-        </is>
-      </c>
-      <c r="F84" s="4" t="inlineStr">
-        <is>
-          <t>30.38%</t>
+          <t>50.00%</t>
+        </is>
+      </c>
+      <c r="E84" s="4" t="inlineStr">
+        <is>
+          <t>55.00%</t>
         </is>
       </c>
     </row>
@@ -6390,27 +5625,22 @@
       </c>
       <c r="B85" s="2" t="inlineStr">
         <is>
-          <t>24.63%</t>
+          <t>0.00%</t>
         </is>
       </c>
       <c r="C85" s="2" t="inlineStr">
         <is>
-          <t>26.17%</t>
+          <t>27.27%</t>
         </is>
       </c>
       <c r="D85" s="2" t="inlineStr">
         <is>
-          <t>11.59%</t>
-        </is>
-      </c>
-      <c r="E85" s="2" t="inlineStr">
-        <is>
-          <t>5.71%</t>
-        </is>
-      </c>
-      <c r="F85" s="4" t="inlineStr">
-        <is>
-          <t>19.17%</t>
+          <t>45.45%</t>
+        </is>
+      </c>
+      <c r="E85" s="4" t="inlineStr">
+        <is>
+          <t>34.78%</t>
         </is>
       </c>
     </row>
@@ -6422,27 +5652,22 @@
       </c>
       <c r="B86" s="4" t="inlineStr">
         <is>
-          <t>30.25%</t>
+          <t>40.43%</t>
         </is>
       </c>
       <c r="C86" s="4" t="inlineStr">
         <is>
-          <t>31.53%</t>
+          <t>50.00%</t>
         </is>
       </c>
       <c r="D86" s="4" t="inlineStr">
         <is>
-          <t>19.06%</t>
+          <t>50.00%</t>
         </is>
       </c>
       <c r="E86" s="4" t="inlineStr">
         <is>
-          <t>16.08%</t>
-        </is>
-      </c>
-      <c r="F86" s="4" t="inlineStr">
-        <is>
-          <t>28.64%</t>
+          <t>45.45%</t>
         </is>
       </c>
     </row>
@@ -6478,11 +5703,6 @@
       </c>
       <c r="E90" s="1" t="inlineStr">
         <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="F90" s="1" t="inlineStr">
-        <is>
           <t>Total</t>
         </is>
       </c>
@@ -6495,27 +5715,22 @@
       </c>
       <c r="B91" s="2" t="inlineStr">
         <is>
-          <t>68.59%</t>
+          <t>61.29%</t>
         </is>
       </c>
       <c r="C91" s="2" t="inlineStr">
         <is>
-          <t>66.70%</t>
+          <t>50.00%</t>
         </is>
       </c>
       <c r="D91" s="2" t="inlineStr">
         <is>
-          <t>73.41%</t>
-        </is>
-      </c>
-      <c r="E91" s="2" t="inlineStr">
-        <is>
-          <t>75.29%</t>
-        </is>
-      </c>
-      <c r="F91" s="4" t="inlineStr">
-        <is>
-          <t>68.36%</t>
+          <t>0.00%</t>
+        </is>
+      </c>
+      <c r="E91" s="4" t="inlineStr">
+        <is>
+          <t>58.33%</t>
         </is>
       </c>
     </row>
@@ -6527,27 +5742,22 @@
       </c>
       <c r="B92" s="2" t="inlineStr">
         <is>
-          <t>70.91%</t>
+          <t>53.33%</t>
         </is>
       </c>
       <c r="C92" s="2" t="inlineStr">
         <is>
-          <t>67.24%</t>
+          <t>36.84%</t>
         </is>
       </c>
       <c r="D92" s="2" t="inlineStr">
         <is>
-          <t>73.30%</t>
-        </is>
-      </c>
-      <c r="E92" s="2" t="inlineStr">
-        <is>
-          <t>84.00%</t>
-        </is>
-      </c>
-      <c r="F92" s="4" t="inlineStr">
-        <is>
-          <t>69.62%</t>
+          <t>50.00%</t>
+        </is>
+      </c>
+      <c r="E92" s="4" t="inlineStr">
+        <is>
+          <t>45.00%</t>
         </is>
       </c>
     </row>
@@ -6559,27 +5769,22 @@
       </c>
       <c r="B93" s="2" t="inlineStr">
         <is>
-          <t>75.37%</t>
+          <t>100.00%</t>
         </is>
       </c>
       <c r="C93" s="2" t="inlineStr">
         <is>
-          <t>73.83%</t>
+          <t>72.73%</t>
         </is>
       </c>
       <c r="D93" s="2" t="inlineStr">
         <is>
-          <t>88.41%</t>
-        </is>
-      </c>
-      <c r="E93" s="2" t="inlineStr">
-        <is>
-          <t>94.29%</t>
-        </is>
-      </c>
-      <c r="F93" s="4" t="inlineStr">
-        <is>
-          <t>80.83%</t>
+          <t>54.55%</t>
+        </is>
+      </c>
+      <c r="E93" s="4" t="inlineStr">
+        <is>
+          <t>65.22%</t>
         </is>
       </c>
     </row>
@@ -6591,27 +5796,22 @@
       </c>
       <c r="B94" s="4" t="inlineStr">
         <is>
-          <t>69.75%</t>
+          <t>59.57%</t>
         </is>
       </c>
       <c r="C94" s="4" t="inlineStr">
         <is>
-          <t>68.47%</t>
+          <t>50.00%</t>
         </is>
       </c>
       <c r="D94" s="4" t="inlineStr">
         <is>
-          <t>80.94%</t>
+          <t>50.00%</t>
         </is>
       </c>
       <c r="E94" s="4" t="inlineStr">
         <is>
-          <t>83.92%</t>
-        </is>
-      </c>
-      <c r="F94" s="4" t="inlineStr">
-        <is>
-          <t>71.36%</t>
+          <t>54.55%</t>
         </is>
       </c>
     </row>
@@ -6647,11 +5847,6 @@
       </c>
       <c r="E98" s="1" t="inlineStr">
         <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="F98" s="1" t="inlineStr">
-        <is>
           <t>Total</t>
         </is>
       </c>
@@ -6677,12 +5872,7 @@
           <t>100.00%</t>
         </is>
       </c>
-      <c r="E99" s="2" t="inlineStr">
-        <is>
-          <t>100.00%</t>
-        </is>
-      </c>
-      <c r="F99" s="4" t="inlineStr">
+      <c r="E99" s="4" t="inlineStr">
         <is>
           <t>100.00%</t>
         </is>
@@ -6709,12 +5899,7 @@
           <t>100.00%</t>
         </is>
       </c>
-      <c r="E100" s="2" t="inlineStr">
-        <is>
-          <t>100.00%</t>
-        </is>
-      </c>
-      <c r="F100" s="4" t="inlineStr">
+      <c r="E100" s="4" t="inlineStr">
         <is>
           <t>100.00%</t>
         </is>
@@ -6741,12 +5926,7 @@
           <t>100.00%</t>
         </is>
       </c>
-      <c r="E101" s="2" t="inlineStr">
-        <is>
-          <t>100.00%</t>
-        </is>
-      </c>
-      <c r="F101" s="4" t="inlineStr">
+      <c r="E101" s="4" t="inlineStr">
         <is>
           <t>100.00%</t>
         </is>
@@ -6774,11 +5954,6 @@
         </is>
       </c>
       <c r="E102" s="4" t="inlineStr">
-        <is>
-          <t>100.00%</t>
-        </is>
-      </c>
-      <c r="F102" s="4" t="inlineStr">
         <is>
           <t>100.00%</t>
         </is>
@@ -6795,13 +5970,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AK13"/>
+  <dimension ref="A1:AK10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="25" customWidth="1" min="1" max="1"/>
     <col width="28" customWidth="1" min="2" max="2"/>
     <col width="12" customWidth="1" min="3" max="3"/>
-    <col width="23" customWidth="1" min="4" max="4"/>
+    <col width="22" customWidth="1" min="4" max="4"/>
     <col width="25" customWidth="1" min="5" max="5"/>
     <col width="23" customWidth="1" min="6" max="6"/>
     <col width="24" customWidth="1" min="7" max="7"/>
@@ -6821,7 +5996,7 @@
     <col width="20" customWidth="1" min="21" max="21"/>
     <col width="20" customWidth="1" min="22" max="22"/>
     <col width="20" customWidth="1" min="23" max="23"/>
-    <col width="20" customWidth="1" min="24" max="24"/>
+    <col width="19" customWidth="1" min="24" max="24"/>
     <col width="11" customWidth="1" min="25" max="25"/>
     <col width="27" customWidth="1" min="26" max="26"/>
     <col width="26" customWidth="1" min="27" max="27"/>
@@ -7032,88 +6207,88 @@
         <v>1</v>
       </c>
       <c r="C2" s="2" t="n">
-        <v>5480</v>
+        <v>31</v>
       </c>
       <c r="D2" s="2" t="n">
-        <v>0.2422527739710888</v>
+        <v>0.3131313131313131</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>2783</v>
+        <v>25</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>168</v>
+        <v>0</v>
       </c>
       <c r="G2" s="2" t="n">
-        <v>2615</v>
+        <v>25</v>
       </c>
       <c r="H2" s="2" t="n">
-        <v>0.06036651095939633</v>
+        <v>0</v>
       </c>
       <c r="I2" s="2" t="n">
-        <v>5092</v>
+        <v>30</v>
       </c>
       <c r="J2" s="2" t="n">
-        <v>154</v>
+        <v>0</v>
       </c>
       <c r="K2" s="2" t="n">
-        <v>4938</v>
+        <v>30</v>
       </c>
       <c r="L2" s="2" t="n">
-        <v>0.03024351924587588</v>
+        <v>0</v>
       </c>
       <c r="M2" s="2" t="n">
-        <v>186061.58</v>
+        <v>0</v>
       </c>
       <c r="N2" s="2" t="n">
-        <v>6693900</v>
+        <v>33225</v>
       </c>
       <c r="O2" s="2" t="n">
-        <v>0.02779569159981476</v>
+        <v>0</v>
       </c>
       <c r="P2" s="2" t="n">
-        <v>275016.18</v>
+        <v>1068.43</v>
       </c>
       <c r="Q2" s="2" t="n">
-        <v>6693900</v>
+        <v>33225</v>
       </c>
       <c r="R2" s="2" t="n">
-        <v>0.04108459642360955</v>
+        <v>0.0321574115876599</v>
       </c>
       <c r="S2" s="2" t="n">
-        <v>0.05155438793233227</v>
+        <v>0.06154452958383991</v>
       </c>
       <c r="T2" s="2" t="n">
-        <v>2433.243613138686</v>
+        <v>2274.193548387097</v>
       </c>
       <c r="U2" s="2" t="n">
-        <v>1468.108576642336</v>
+        <v>1265.322580645161</v>
       </c>
       <c r="V2" s="2" t="n">
-        <v>1931.059134428223</v>
+        <v>2065.672741935484</v>
       </c>
       <c r="W2" s="2" t="n">
-        <v>1542.28305596107</v>
+        <v>1627.828548387096</v>
       </c>
       <c r="X2" s="2" t="n">
-        <v>8034.173803832115</v>
+        <v>7457.203978494624</v>
       </c>
       <c r="Y2" s="2" t="n">
-        <v>5480</v>
+        <v>31</v>
       </c>
       <c r="Z2" s="2" t="n">
-        <v>5480</v>
+        <v>31</v>
       </c>
       <c r="AA2" s="2" t="n">
-        <v>5480</v>
+        <v>31</v>
       </c>
       <c r="AB2" s="2" t="n">
-        <v>1721</v>
+        <v>12</v>
       </c>
       <c r="AC2" s="2" t="n">
-        <v>3759</v>
+        <v>19</v>
       </c>
       <c r="AD2" s="2" t="n">
-        <v>5480</v>
+        <v>31</v>
       </c>
       <c r="AE2" s="2" t="n">
         <v>1</v>
@@ -7122,16 +6297,16 @@
         <v>1</v>
       </c>
       <c r="AG2" s="2" t="n">
-        <v>0.314051094890511</v>
+        <v>0.3870967741935484</v>
       </c>
       <c r="AH2" s="2" t="n">
-        <v>0.685948905109489</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="AI2" s="2" t="n">
-        <v>0.314051094890511</v>
+        <v>0.3870967741935484</v>
       </c>
       <c r="AJ2" s="2" t="n">
-        <v>0.685948905109489</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="AK2" s="2" t="n">
         <v>1</v>
@@ -7145,88 +6320,88 @@
         <v>2</v>
       </c>
       <c r="C3" s="2" t="n">
-        <v>2670</v>
+        <v>4</v>
       </c>
       <c r="D3" s="2" t="n">
-        <v>0.1180319172450378</v>
+        <v>0.04040404040404041</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>1466</v>
+        <v>3</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>163</v>
+        <v>0</v>
       </c>
       <c r="G3" s="2" t="n">
-        <v>1303</v>
+        <v>3</v>
       </c>
       <c r="H3" s="2" t="n">
-        <v>0.1111869031377899</v>
+        <v>0</v>
       </c>
       <c r="I3" s="2" t="n">
-        <v>2502</v>
+        <v>4</v>
       </c>
       <c r="J3" s="2" t="n">
-        <v>151</v>
+        <v>0</v>
       </c>
       <c r="K3" s="2" t="n">
-        <v>2351</v>
+        <v>4</v>
       </c>
       <c r="L3" s="2" t="n">
-        <v>0.06035171862509992</v>
+        <v>0</v>
       </c>
       <c r="M3" s="2" t="n">
-        <v>184144.33</v>
+        <v>0</v>
       </c>
       <c r="N3" s="2" t="n">
-        <v>2953295</v>
+        <v>3675</v>
       </c>
       <c r="O3" s="2" t="n">
-        <v>0.06235216258450308</v>
+        <v>0</v>
       </c>
       <c r="P3" s="2" t="n">
-        <v>263091.98</v>
+        <v>0</v>
       </c>
       <c r="Q3" s="2" t="n">
-        <v>2953295</v>
+        <v>3675</v>
       </c>
       <c r="R3" s="2" t="n">
-        <v>0.08908421949043356</v>
+        <v>0</v>
       </c>
       <c r="S3" s="2" t="n">
-        <v>0.04767672744666276</v>
+        <v>0.05924058035589727</v>
       </c>
       <c r="T3" s="2" t="n">
-        <v>2514.982397003746</v>
+        <v>3750</v>
       </c>
       <c r="U3" s="2" t="n">
-        <v>1237.685393258427</v>
+        <v>918.75</v>
       </c>
       <c r="V3" s="2" t="n">
-        <v>2554.608674157303</v>
+        <v>1797.81875</v>
       </c>
       <c r="W3" s="2" t="n">
-        <v>2191.619509363296</v>
+        <v>1456.173333333333</v>
       </c>
       <c r="X3" s="2" t="n">
-        <v>8221.790445068664</v>
+        <v>5954.476666666666</v>
       </c>
       <c r="Y3" s="2" t="n">
-        <v>2670</v>
+        <v>4</v>
       </c>
       <c r="Z3" s="2" t="n">
-        <v>2670</v>
+        <v>4</v>
       </c>
       <c r="AA3" s="2" t="n">
-        <v>2670</v>
+        <v>4</v>
       </c>
       <c r="AB3" s="2" t="n">
-        <v>889</v>
+        <v>2</v>
       </c>
       <c r="AC3" s="2" t="n">
-        <v>1781</v>
+        <v>2</v>
       </c>
       <c r="AD3" s="2" t="n">
-        <v>2670</v>
+        <v>4</v>
       </c>
       <c r="AE3" s="2" t="n">
         <v>1</v>
@@ -7235,16 +6410,16 @@
         <v>1</v>
       </c>
       <c r="AG3" s="2" t="n">
-        <v>0.3329588014981273</v>
+        <v>0.5</v>
       </c>
       <c r="AH3" s="2" t="n">
-        <v>0.6670411985018727</v>
+        <v>0.5</v>
       </c>
       <c r="AI3" s="2" t="n">
-        <v>0.3329588014981273</v>
+        <v>0.5</v>
       </c>
       <c r="AJ3" s="2" t="n">
-        <v>0.6670411985018727</v>
+        <v>0.5</v>
       </c>
       <c r="AK3" s="2" t="n">
         <v>1</v>
@@ -7258,88 +6433,88 @@
         <v>3</v>
       </c>
       <c r="C4" s="2" t="n">
-        <v>504</v>
+        <v>1</v>
       </c>
       <c r="D4" s="2" t="n">
-        <v>0.02228018213164758</v>
+        <v>0.0101010101010101</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>397</v>
+        <v>1</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>49</v>
+        <v>0</v>
       </c>
       <c r="G4" s="2" t="n">
-        <v>348</v>
+        <v>1</v>
       </c>
       <c r="H4" s="2" t="n">
-        <v>0.1234256926952141</v>
+        <v>0</v>
       </c>
       <c r="I4" s="2" t="n">
-        <v>504</v>
+        <v>1</v>
       </c>
       <c r="J4" s="2" t="n">
-        <v>47</v>
+        <v>0</v>
       </c>
       <c r="K4" s="2" t="n">
-        <v>457</v>
+        <v>1</v>
       </c>
       <c r="L4" s="2" t="n">
-        <v>0.09325396825396826</v>
+        <v>0</v>
       </c>
       <c r="M4" s="2" t="n">
-        <v>58785.41</v>
+        <v>0</v>
       </c>
       <c r="N4" s="2" t="n">
-        <v>674375</v>
+        <v>1725</v>
       </c>
       <c r="O4" s="2" t="n">
-        <v>0.08717020945319741</v>
+        <v>0</v>
       </c>
       <c r="P4" s="2" t="n">
-        <v>75555.34</v>
+        <v>0</v>
       </c>
       <c r="Q4" s="2" t="n">
-        <v>674375</v>
+        <v>1725</v>
       </c>
       <c r="R4" s="2" t="n">
-        <v>0.1120375755329008</v>
+        <v>0</v>
       </c>
       <c r="S4" s="2" t="n">
-        <v>0.04542985628806908</v>
+        <v>0.0883014953417364</v>
       </c>
       <c r="T4" s="2" t="n">
-        <v>2572.24007936508</v>
+        <v>2800</v>
       </c>
       <c r="U4" s="2" t="n">
-        <v>1338.045634920635</v>
+        <v>1725</v>
       </c>
       <c r="V4" s="2" t="n">
-        <v>3525.184894179894</v>
+        <v>6621.896666666667</v>
       </c>
       <c r="W4" s="2" t="n">
-        <v>3135.597377645502</v>
+        <v>5839.903333333333</v>
       </c>
       <c r="X4" s="2" t="n">
-        <v>9406.976643518519</v>
+        <v>8855.946666666665</v>
       </c>
       <c r="Y4" s="2" t="n">
-        <v>504</v>
+        <v>1</v>
       </c>
       <c r="Z4" s="2" t="n">
-        <v>504</v>
+        <v>1</v>
       </c>
       <c r="AA4" s="2" t="n">
-        <v>504</v>
+        <v>1</v>
       </c>
       <c r="AB4" s="2" t="n">
-        <v>134</v>
+        <v>1</v>
       </c>
       <c r="AC4" s="2" t="n">
-        <v>370</v>
+        <v>0</v>
       </c>
       <c r="AD4" s="2" t="n">
-        <v>504</v>
+        <v>1</v>
       </c>
       <c r="AE4" s="2" t="n">
         <v>1</v>
@@ -7348,16 +6523,16 @@
         <v>1</v>
       </c>
       <c r="AG4" s="2" t="n">
-        <v>0.2658730158730159</v>
+        <v>1</v>
       </c>
       <c r="AH4" s="2" t="n">
-        <v>0.7341269841269841</v>
+        <v>0</v>
       </c>
       <c r="AI4" s="2" t="n">
-        <v>0.2658730158730159</v>
+        <v>1</v>
       </c>
       <c r="AJ4" s="2" t="n">
-        <v>0.7341269841269841</v>
+        <v>0</v>
       </c>
       <c r="AK4" s="2" t="n">
         <v>1</v>
@@ -7365,44 +6540,46 @@
     </row>
     <row r="5">
       <c r="A5" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="B5" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="B5" s="2" t="n"/>
       <c r="C5" s="2" t="n">
-        <v>85</v>
+        <v>15</v>
       </c>
       <c r="D5" s="2" t="n">
-        <v>0.003757570399186597</v>
+        <v>0.1515151515151515</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="F5" s="2" t="n">
         <v>0</v>
       </c>
       <c r="G5" s="2" t="n">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="H5" s="2" t="n">
         <v>0</v>
       </c>
       <c r="I5" s="2" t="n">
-        <v>69</v>
+        <v>15</v>
       </c>
       <c r="J5" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K5" s="2" t="n">
-        <v>68</v>
+        <v>15</v>
       </c>
       <c r="L5" s="2" t="n">
-        <v>0.01449275362318841</v>
+        <v>0</v>
       </c>
       <c r="M5" s="2" t="n">
         <v>0</v>
       </c>
       <c r="N5" s="2" t="n">
-        <v>109525</v>
+        <v>13425</v>
       </c>
       <c r="O5" s="2" t="n">
         <v>0</v>
@@ -7411,46 +6588,46 @@
         <v>0</v>
       </c>
       <c r="Q5" s="2" t="n">
-        <v>109525</v>
+        <v>13425</v>
       </c>
       <c r="R5" s="2" t="n">
         <v>0</v>
       </c>
       <c r="S5" s="2" t="n">
-        <v>0.05335271283470183</v>
+        <v>0.06163662244143231</v>
       </c>
       <c r="T5" s="2" t="n">
-        <v>2491.176470588235</v>
+        <v>1958.333333333333</v>
       </c>
       <c r="U5" s="2" t="n">
-        <v>1555.588235294118</v>
+        <v>895</v>
       </c>
       <c r="V5" s="2" t="n">
-        <v>3240.892352941176</v>
+        <v>1231.295</v>
       </c>
       <c r="W5" s="2" t="n">
-        <v>2844.129294117647</v>
+        <v>905.4875555555554</v>
       </c>
       <c r="X5" s="2" t="n">
-        <v>8982.372431372549</v>
+        <v>5538.863777777778</v>
       </c>
       <c r="Y5" s="2" t="n">
-        <v>85</v>
+        <v>15</v>
       </c>
       <c r="Z5" s="2" t="n">
-        <v>85</v>
+        <v>15</v>
       </c>
       <c r="AA5" s="2" t="n">
-        <v>85</v>
+        <v>15</v>
       </c>
       <c r="AB5" s="2" t="n">
-        <v>21</v>
+        <v>7</v>
       </c>
       <c r="AC5" s="2" t="n">
-        <v>64</v>
+        <v>8</v>
       </c>
       <c r="AD5" s="2" t="n">
-        <v>85</v>
+        <v>15</v>
       </c>
       <c r="AE5" s="2" t="n">
         <v>1</v>
@@ -7459,16 +6636,16 @@
         <v>1</v>
       </c>
       <c r="AG5" s="2" t="n">
-        <v>0.2470588235294118</v>
+        <v>0.4666666666666667</v>
       </c>
       <c r="AH5" s="2" t="n">
-        <v>0.7529411764705882</v>
+        <v>0.5333333333333333</v>
       </c>
       <c r="AI5" s="2" t="n">
-        <v>0.2470588235294118</v>
+        <v>0.4666666666666667</v>
       </c>
       <c r="AJ5" s="2" t="n">
-        <v>0.7529411764705882</v>
+        <v>0.5333333333333333</v>
       </c>
       <c r="AK5" s="2" t="n">
         <v>1</v>
@@ -7479,91 +6656,91 @@
         <v>2</v>
       </c>
       <c r="B6" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="C6" s="2" t="n">
+        <v>19</v>
+      </c>
+      <c r="D6" s="2" t="n">
+        <v>0.1919191919191919</v>
+      </c>
+      <c r="E6" s="2" t="n">
+        <v>16</v>
+      </c>
+      <c r="F6" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="G6" s="2" t="n">
+        <v>14</v>
+      </c>
+      <c r="H6" s="2" t="n">
+        <v>0.125</v>
+      </c>
+      <c r="I6" s="2" t="n">
+        <v>19</v>
+      </c>
+      <c r="J6" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="C6" s="2" t="n">
-        <v>3200</v>
-      </c>
-      <c r="D6" s="2" t="n">
-        <v>0.1414614738517307</v>
-      </c>
-      <c r="E6" s="2" t="n">
-        <v>1473</v>
-      </c>
-      <c r="F6" s="2" t="n">
-        <v>119</v>
-      </c>
-      <c r="G6" s="2" t="n">
-        <v>1354</v>
-      </c>
-      <c r="H6" s="2" t="n">
-        <v>0.08078750848608282</v>
-      </c>
-      <c r="I6" s="2" t="n">
-        <v>2897</v>
-      </c>
-      <c r="J6" s="2" t="n">
-        <v>115</v>
-      </c>
       <c r="K6" s="2" t="n">
-        <v>2782</v>
+        <v>18</v>
       </c>
       <c r="L6" s="2" t="n">
-        <v>0.03969623748705557</v>
+        <v>0.05263157894736842</v>
       </c>
       <c r="M6" s="2" t="n">
-        <v>95551.26999999999</v>
+        <v>2945.06</v>
       </c>
       <c r="N6" s="2" t="n">
-        <v>2822471</v>
+        <v>20075</v>
       </c>
       <c r="O6" s="2" t="n">
-        <v>0.03385376501654046</v>
+        <v>0.1467028642590286</v>
       </c>
       <c r="P6" s="2" t="n">
-        <v>159584.34</v>
+        <v>2647.62</v>
       </c>
       <c r="Q6" s="2" t="n">
-        <v>2822471</v>
+        <v>20075</v>
       </c>
       <c r="R6" s="2" t="n">
-        <v>0.05654064824758163</v>
+        <v>0.1318864259028643</v>
       </c>
       <c r="S6" s="2" t="n">
-        <v>0.04923409267834576</v>
+        <v>0.06076568309818389</v>
       </c>
       <c r="T6" s="2" t="n">
-        <v>2054.09375</v>
+        <v>2603.947368421052</v>
       </c>
       <c r="U6" s="2" t="n">
-        <v>1126.3346875</v>
+        <v>1056.578947368421</v>
       </c>
       <c r="V6" s="2" t="n">
-        <v>1317.569202083333</v>
+        <v>2178.835350877193</v>
       </c>
       <c r="W6" s="2" t="n">
-        <v>1041.780025</v>
+        <v>1809.440350877193</v>
       </c>
       <c r="X6" s="2" t="n">
-        <v>5949.089778125</v>
+        <v>6692.273421052631</v>
       </c>
       <c r="Y6" s="2" t="n">
-        <v>3200</v>
+        <v>19</v>
       </c>
       <c r="Z6" s="2" t="n">
-        <v>3200</v>
+        <v>19</v>
       </c>
       <c r="AA6" s="2" t="n">
-        <v>3200</v>
+        <v>19</v>
       </c>
       <c r="AB6" s="2" t="n">
-        <v>931</v>
+        <v>12</v>
       </c>
       <c r="AC6" s="2" t="n">
-        <v>2269</v>
+        <v>7</v>
       </c>
       <c r="AD6" s="2" t="n">
-        <v>3200</v>
+        <v>19</v>
       </c>
       <c r="AE6" s="2" t="n">
         <v>1</v>
@@ -7572,16 +6749,16 @@
         <v>1</v>
       </c>
       <c r="AG6" s="2" t="n">
-        <v>0.2909375</v>
+        <v>0.631578947368421</v>
       </c>
       <c r="AH6" s="2" t="n">
-        <v>0.7090625</v>
+        <v>0.3684210526315789</v>
       </c>
       <c r="AI6" s="2" t="n">
-        <v>0.2909375</v>
+        <v>0.631578947368421</v>
       </c>
       <c r="AJ6" s="2" t="n">
-        <v>0.7090625</v>
+        <v>0.3684210526315789</v>
       </c>
       <c r="AK6" s="2" t="n">
         <v>1</v>
@@ -7592,91 +6769,91 @@
         <v>2</v>
       </c>
       <c r="B7" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C7" s="2" t="n">
-        <v>4609</v>
+        <v>6</v>
       </c>
       <c r="D7" s="2" t="n">
-        <v>0.2037487290570709</v>
+        <v>0.06060606060606061</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>2479</v>
+        <v>6</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>330</v>
+        <v>0</v>
       </c>
       <c r="G7" s="2" t="n">
-        <v>2149</v>
+        <v>6</v>
       </c>
       <c r="H7" s="2" t="n">
-        <v>0.1331181928196853</v>
+        <v>0</v>
       </c>
       <c r="I7" s="2" t="n">
-        <v>4251</v>
+        <v>6</v>
       </c>
       <c r="J7" s="2" t="n">
-        <v>339</v>
+        <v>0</v>
       </c>
       <c r="K7" s="2" t="n">
-        <v>3912</v>
+        <v>6</v>
       </c>
       <c r="L7" s="2" t="n">
-        <v>0.07974594213126324</v>
+        <v>0</v>
       </c>
       <c r="M7" s="2" t="n">
-        <v>281608.84</v>
+        <v>0</v>
       </c>
       <c r="N7" s="2" t="n">
-        <v>3659691</v>
+        <v>4225</v>
       </c>
       <c r="O7" s="2" t="n">
-        <v>0.07694880250818989</v>
+        <v>0</v>
       </c>
       <c r="P7" s="2" t="n">
-        <v>356612.67</v>
+        <v>352.94</v>
       </c>
       <c r="Q7" s="2" t="n">
-        <v>3659691</v>
+        <v>4225</v>
       </c>
       <c r="R7" s="2" t="n">
-        <v>0.09744338251508121</v>
+        <v>0.08353609467455621</v>
       </c>
       <c r="S7" s="2" t="n">
-        <v>0.04387744357646557</v>
+        <v>0.04846571286640807</v>
       </c>
       <c r="T7" s="2" t="n">
-        <v>2026.091343024517</v>
+        <v>1433.333333333333</v>
       </c>
       <c r="U7" s="2" t="n">
-        <v>924.7235842916034</v>
+        <v>704.1666666666666</v>
       </c>
       <c r="V7" s="2" t="n">
-        <v>1634.292508497866</v>
+        <v>1710.215</v>
       </c>
       <c r="W7" s="2" t="n">
-        <v>1385.619525927533</v>
+        <v>1415.172777777778</v>
       </c>
       <c r="X7" s="2" t="n">
-        <v>6057.573859116222</v>
+        <v>6239.739999999999</v>
       </c>
       <c r="Y7" s="2" t="n">
-        <v>4609</v>
+        <v>6</v>
       </c>
       <c r="Z7" s="2" t="n">
-        <v>4609</v>
+        <v>6</v>
       </c>
       <c r="AA7" s="2" t="n">
-        <v>4609</v>
+        <v>6</v>
       </c>
       <c r="AB7" s="2" t="n">
-        <v>1510</v>
+        <v>3</v>
       </c>
       <c r="AC7" s="2" t="n">
-        <v>3099</v>
+        <v>3</v>
       </c>
       <c r="AD7" s="2" t="n">
-        <v>4609</v>
+        <v>6</v>
       </c>
       <c r="AE7" s="2" t="n">
         <v>1</v>
@@ -7685,16 +6862,16 @@
         <v>1</v>
       </c>
       <c r="AG7" s="2" t="n">
-        <v>0.3276198741592536</v>
+        <v>0.5</v>
       </c>
       <c r="AH7" s="2" t="n">
-        <v>0.6723801258407464</v>
+        <v>0.5</v>
       </c>
       <c r="AI7" s="2" t="n">
-        <v>0.3276198741592536</v>
+        <v>0.5</v>
       </c>
       <c r="AJ7" s="2" t="n">
-        <v>0.6723801258407464</v>
+        <v>0.5</v>
       </c>
       <c r="AK7" s="2" t="n">
         <v>1</v>
@@ -7702,94 +6879,94 @@
     </row>
     <row r="8">
       <c r="A8" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B8" s="2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C8" s="2" t="n">
-        <v>1472</v>
+        <v>1</v>
       </c>
       <c r="D8" s="2" t="n">
-        <v>0.06507227797179611</v>
+        <v>0.0101010101010101</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>1136</v>
+        <v>1</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>211</v>
+        <v>0</v>
       </c>
       <c r="G8" s="2" t="n">
-        <v>925</v>
+        <v>1</v>
       </c>
       <c r="H8" s="2" t="n">
-        <v>0.1857394366197183</v>
+        <v>0</v>
       </c>
       <c r="I8" s="2" t="n">
-        <v>1472</v>
+        <v>1</v>
       </c>
       <c r="J8" s="2" t="n">
-        <v>158</v>
+        <v>0</v>
       </c>
       <c r="K8" s="2" t="n">
-        <v>1314</v>
+        <v>1</v>
       </c>
       <c r="L8" s="2" t="n">
-        <v>0.1073369565217391</v>
+        <v>0</v>
       </c>
       <c r="M8" s="2" t="n">
-        <v>183776.86</v>
+        <v>0</v>
       </c>
       <c r="N8" s="2" t="n">
-        <v>1443598</v>
+        <v>500</v>
       </c>
       <c r="O8" s="2" t="n">
-        <v>0.1273047344205243</v>
+        <v>0</v>
       </c>
       <c r="P8" s="2" t="n">
-        <v>225991.67</v>
+        <v>0</v>
       </c>
       <c r="Q8" s="2" t="n">
-        <v>1443598</v>
+        <v>500</v>
       </c>
       <c r="R8" s="2" t="n">
-        <v>0.1565475083783713</v>
+        <v>0</v>
       </c>
       <c r="S8" s="2" t="n">
-        <v>0.0426884086091251</v>
+        <v>0.0303980241284316</v>
       </c>
       <c r="T8" s="2" t="n">
-        <v>2080.947690217391</v>
+        <v>2050</v>
       </c>
       <c r="U8" s="2" t="n">
-        <v>980.7051630434783</v>
+        <v>500</v>
       </c>
       <c r="V8" s="2" t="n">
-        <v>2092.104895833333</v>
+        <v>1990.17</v>
       </c>
       <c r="W8" s="2" t="n">
-        <v>1829.730129076087</v>
+        <v>1712.836666666667</v>
       </c>
       <c r="X8" s="2" t="n">
-        <v>6600.021767436592</v>
+        <v>9123.4</v>
       </c>
       <c r="Y8" s="2" t="n">
-        <v>1472</v>
+        <v>1</v>
       </c>
       <c r="Z8" s="2" t="n">
-        <v>1472</v>
+        <v>1</v>
       </c>
       <c r="AA8" s="2" t="n">
-        <v>1472</v>
+        <v>1</v>
       </c>
       <c r="AB8" s="2" t="n">
-        <v>393</v>
+        <v>0</v>
       </c>
       <c r="AC8" s="2" t="n">
-        <v>1079</v>
+        <v>1</v>
       </c>
       <c r="AD8" s="2" t="n">
-        <v>1472</v>
+        <v>1</v>
       </c>
       <c r="AE8" s="2" t="n">
         <v>1</v>
@@ -7798,16 +6975,16 @@
         <v>1</v>
       </c>
       <c r="AG8" s="2" t="n">
-        <v>0.2669836956521739</v>
+        <v>0</v>
       </c>
       <c r="AH8" s="2" t="n">
-        <v>0.7330163043478261</v>
+        <v>1</v>
       </c>
       <c r="AI8" s="2" t="n">
-        <v>0.2669836956521739</v>
+        <v>0</v>
       </c>
       <c r="AJ8" s="2" t="n">
-        <v>0.7330163043478261</v>
+        <v>1</v>
       </c>
       <c r="AK8" s="2" t="n">
         <v>1</v>
@@ -7815,90 +6992,94 @@
     </row>
     <row r="9">
       <c r="A9" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="B9" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="B9" s="2" t="n"/>
       <c r="C9" s="2" t="n">
-        <v>100</v>
+        <v>11</v>
       </c>
       <c r="D9" s="2" t="n">
-        <v>0.004420671057866584</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="F9" s="2" t="n">
         <v>0</v>
       </c>
       <c r="G9" s="2" t="n">
+        <v>11</v>
+      </c>
+      <c r="H9" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="H9" s="2" t="n"/>
       <c r="I9" s="2" t="n">
-        <v>81</v>
+        <v>11</v>
       </c>
       <c r="J9" s="2" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="K9" s="2" t="n">
-        <v>75</v>
+        <v>10</v>
       </c>
       <c r="L9" s="2" t="n">
-        <v>0.07407407407407407</v>
+        <v>0.09090909090909091</v>
       </c>
       <c r="M9" s="2" t="n">
         <v>0</v>
       </c>
       <c r="N9" s="2" t="n">
-        <v>88925</v>
+        <v>9325</v>
       </c>
       <c r="O9" s="2" t="n">
         <v>0</v>
       </c>
       <c r="P9" s="2" t="n">
-        <v>2158.73</v>
+        <v>0</v>
       </c>
       <c r="Q9" s="2" t="n">
-        <v>88925</v>
+        <v>9325</v>
       </c>
       <c r="R9" s="2" t="n">
-        <v>0.02427585043576047</v>
+        <v>0</v>
       </c>
       <c r="S9" s="2" t="n">
-        <v>0.04828971443647235</v>
+        <v>0.05767748073146366</v>
       </c>
       <c r="T9" s="2" t="n">
-        <v>2315</v>
+        <v>2290.909090909091</v>
       </c>
       <c r="U9" s="2" t="n">
-        <v>1257.5</v>
+        <v>847.7272727272727</v>
       </c>
       <c r="V9" s="2" t="n">
-        <v>1554.621683333333</v>
+        <v>2203.679242424242</v>
       </c>
       <c r="W9" s="2" t="n">
-        <v>1275.105</v>
+        <v>1904.637878787878</v>
       </c>
       <c r="X9" s="2" t="n">
-        <v>6035.733816666666</v>
+        <v>5929.262575757574</v>
       </c>
       <c r="Y9" s="2" t="n">
-        <v>100</v>
+        <v>11</v>
       </c>
       <c r="Z9" s="2" t="n">
-        <v>100</v>
+        <v>11</v>
       </c>
       <c r="AA9" s="2" t="n">
-        <v>100</v>
+        <v>11</v>
       </c>
       <c r="AB9" s="2" t="n">
-        <v>16</v>
+        <v>3</v>
       </c>
       <c r="AC9" s="2" t="n">
-        <v>84</v>
+        <v>8</v>
       </c>
       <c r="AD9" s="2" t="n">
-        <v>100</v>
+        <v>11</v>
       </c>
       <c r="AE9" s="2" t="n">
         <v>1</v>
@@ -7907,16 +7088,16 @@
         <v>1</v>
       </c>
       <c r="AG9" s="2" t="n">
-        <v>0.16</v>
+        <v>0.2727272727272727</v>
       </c>
       <c r="AH9" s="2" t="n">
-        <v>0.84</v>
+        <v>0.7272727272727273</v>
       </c>
       <c r="AI9" s="2" t="n">
-        <v>0.16</v>
+        <v>0.2727272727272727</v>
       </c>
       <c r="AJ9" s="2" t="n">
-        <v>0.84</v>
+        <v>0.7272727272727273</v>
       </c>
       <c r="AK9" s="2" t="n">
         <v>1</v>
@@ -7927,91 +7108,91 @@
         <v>3</v>
       </c>
       <c r="B10" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C10" s="2" t="n">
-        <v>475</v>
+        <v>11</v>
       </c>
       <c r="D10" s="2" t="n">
-        <v>0.02099818752486627</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>178</v>
+        <v>10</v>
       </c>
       <c r="F10" s="2" t="n">
-        <v>18</v>
+        <v>3</v>
       </c>
       <c r="G10" s="2" t="n">
-        <v>160</v>
+        <v>7</v>
       </c>
       <c r="H10" s="2" t="n">
-        <v>0.101123595505618</v>
+        <v>0.3</v>
       </c>
       <c r="I10" s="2" t="n">
-        <v>428</v>
+        <v>11</v>
       </c>
       <c r="J10" s="2" t="n">
-        <v>29</v>
+        <v>2</v>
       </c>
       <c r="K10" s="2" t="n">
-        <v>399</v>
+        <v>9</v>
       </c>
       <c r="L10" s="2" t="n">
-        <v>0.06775700934579439</v>
+        <v>0.1818181818181818</v>
       </c>
       <c r="M10" s="2" t="n">
-        <v>11348.85</v>
+        <v>1495.57</v>
       </c>
       <c r="N10" s="2" t="n">
-        <v>293200</v>
+        <v>7925</v>
       </c>
       <c r="O10" s="2" t="n">
-        <v>0.03870685538881309</v>
+        <v>0.1887154574132492</v>
       </c>
       <c r="P10" s="2" t="n">
-        <v>20644.24</v>
+        <v>2122.93</v>
       </c>
       <c r="Q10" s="2" t="n">
-        <v>293200</v>
+        <v>7925</v>
       </c>
       <c r="R10" s="2" t="n">
-        <v>0.07041009549795361</v>
+        <v>0.2678776025236593</v>
       </c>
       <c r="S10" s="2" t="n">
-        <v>0.04288214043019844</v>
+        <v>0.05840024437431996</v>
       </c>
       <c r="T10" s="2" t="n">
-        <v>1615.894736842105</v>
+        <v>1586.363636363636</v>
       </c>
       <c r="U10" s="2" t="n">
-        <v>820.6842105263158</v>
+        <v>720.4545454545455</v>
       </c>
       <c r="V10" s="2" t="n">
-        <v>1025.551115789474</v>
+        <v>1592.921515151515</v>
       </c>
       <c r="W10" s="2" t="n">
-        <v>825.8625859649122</v>
+        <v>1322.805151515151</v>
       </c>
       <c r="X10" s="2" t="n">
-        <v>4941.925596491228</v>
+        <v>5040.430909090909</v>
       </c>
       <c r="Y10" s="2" t="n">
-        <v>475</v>
+        <v>11</v>
       </c>
       <c r="Z10" s="2" t="n">
-        <v>475</v>
+        <v>11</v>
       </c>
       <c r="AA10" s="2" t="n">
-        <v>475</v>
+        <v>11</v>
       </c>
       <c r="AB10" s="2" t="n">
-        <v>117</v>
+        <v>5</v>
       </c>
       <c r="AC10" s="2" t="n">
-        <v>358</v>
+        <v>6</v>
       </c>
       <c r="AD10" s="2" t="n">
-        <v>475</v>
+        <v>11</v>
       </c>
       <c r="AE10" s="2" t="n">
         <v>1</v>
@@ -8020,355 +7201,18 @@
         <v>1</v>
       </c>
       <c r="AG10" s="2" t="n">
-        <v>0.2463157894736842</v>
+        <v>0.4545454545454545</v>
       </c>
       <c r="AH10" s="2" t="n">
-        <v>0.7536842105263157</v>
+        <v>0.5454545454545454</v>
       </c>
       <c r="AI10" s="2" t="n">
-        <v>0.2463157894736842</v>
+        <v>0.4545454545454545</v>
       </c>
       <c r="AJ10" s="2" t="n">
-        <v>0.7536842105263157</v>
+        <v>0.5454545454545454</v>
       </c>
       <c r="AK10" s="2" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="B11" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="C11" s="2" t="n">
-        <v>1945</v>
-      </c>
-      <c r="D11" s="2" t="n">
-        <v>0.08598205207550506</v>
-      </c>
-      <c r="E11" s="2" t="n">
-        <v>900</v>
-      </c>
-      <c r="F11" s="2" t="n">
-        <v>160</v>
-      </c>
-      <c r="G11" s="2" t="n">
-        <v>740</v>
-      </c>
-      <c r="H11" s="2" t="n">
-        <v>0.1777777777777778</v>
-      </c>
-      <c r="I11" s="2" t="n">
-        <v>1777</v>
-      </c>
-      <c r="J11" s="2" t="n">
-        <v>185</v>
-      </c>
-      <c r="K11" s="2" t="n">
-        <v>1592</v>
-      </c>
-      <c r="L11" s="2" t="n">
-        <v>0.1041080472706809</v>
-      </c>
-      <c r="M11" s="2" t="n">
-        <v>105766.69</v>
-      </c>
-      <c r="N11" s="2" t="n">
-        <v>1134788</v>
-      </c>
-      <c r="O11" s="2" t="n">
-        <v>0.09320392002735313</v>
-      </c>
-      <c r="P11" s="2" t="n">
-        <v>144899.84</v>
-      </c>
-      <c r="Q11" s="2" t="n">
-        <v>1134788</v>
-      </c>
-      <c r="R11" s="2" t="n">
-        <v>0.127688907531627</v>
-      </c>
-      <c r="S11" s="2" t="n">
-        <v>0.03998917130724979</v>
-      </c>
-      <c r="T11" s="2" t="n">
-        <v>1729.807712082262</v>
-      </c>
-      <c r="U11" s="2" t="n">
-        <v>722.5645244215938</v>
-      </c>
-      <c r="V11" s="2" t="n">
-        <v>1298.539087403599</v>
-      </c>
-      <c r="W11" s="2" t="n">
-        <v>1110.423138817481</v>
-      </c>
-      <c r="X11" s="2" t="n">
-        <v>4995.381726649529</v>
-      </c>
-      <c r="Y11" s="2" t="n">
-        <v>1945</v>
-      </c>
-      <c r="Z11" s="2" t="n">
-        <v>1945</v>
-      </c>
-      <c r="AA11" s="2" t="n">
-        <v>1945</v>
-      </c>
-      <c r="AB11" s="2" t="n">
-        <v>509</v>
-      </c>
-      <c r="AC11" s="2" t="n">
-        <v>1436</v>
-      </c>
-      <c r="AD11" s="2" t="n">
-        <v>1945</v>
-      </c>
-      <c r="AE11" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="AF11" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="AG11" s="2" t="n">
-        <v>0.2616966580976864</v>
-      </c>
-      <c r="AH11" s="2" t="n">
-        <v>0.7383033419023136</v>
-      </c>
-      <c r="AI11" s="2" t="n">
-        <v>0.2616966580976864</v>
-      </c>
-      <c r="AJ11" s="2" t="n">
-        <v>0.7383033419023136</v>
-      </c>
-      <c r="AK11" s="2" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="B12" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="C12" s="2" t="n">
-        <v>2011</v>
-      </c>
-      <c r="D12" s="2" t="n">
-        <v>0.08889969497369701</v>
-      </c>
-      <c r="E12" s="2" t="n">
-        <v>1536</v>
-      </c>
-      <c r="F12" s="2" t="n">
-        <v>411</v>
-      </c>
-      <c r="G12" s="2" t="n">
-        <v>1125</v>
-      </c>
-      <c r="H12" s="2" t="n">
-        <v>0.267578125</v>
-      </c>
-      <c r="I12" s="2" t="n">
-        <v>2011</v>
-      </c>
-      <c r="J12" s="2" t="n">
-        <v>287</v>
-      </c>
-      <c r="K12" s="2" t="n">
-        <v>1724</v>
-      </c>
-      <c r="L12" s="2" t="n">
-        <v>0.1427150671307807</v>
-      </c>
-      <c r="M12" s="2" t="n">
-        <v>275285.61</v>
-      </c>
-      <c r="N12" s="2" t="n">
-        <v>1552999</v>
-      </c>
-      <c r="O12" s="2" t="n">
-        <v>0.1772606485902438</v>
-      </c>
-      <c r="P12" s="2" t="n">
-        <v>337727.28</v>
-      </c>
-      <c r="Q12" s="2" t="n">
-        <v>1552999</v>
-      </c>
-      <c r="R12" s="2" t="n">
-        <v>0.2174678026193192</v>
-      </c>
-      <c r="S12" s="2" t="n">
-        <v>0.03744913627102454</v>
-      </c>
-      <c r="T12" s="2" t="n">
-        <v>1854.62506215813</v>
-      </c>
-      <c r="U12" s="2" t="n">
-        <v>772.2521133764296</v>
-      </c>
-      <c r="V12" s="2" t="n">
-        <v>1611.858859605503</v>
-      </c>
-      <c r="W12" s="2" t="n">
-        <v>1418.838822310625</v>
-      </c>
-      <c r="X12" s="2" t="n">
-        <v>5474.728495773246</v>
-      </c>
-      <c r="Y12" s="2" t="n">
-        <v>2011</v>
-      </c>
-      <c r="Z12" s="2" t="n">
-        <v>2011</v>
-      </c>
-      <c r="AA12" s="2" t="n">
-        <v>2011</v>
-      </c>
-      <c r="AB12" s="2" t="n">
-        <v>233</v>
-      </c>
-      <c r="AC12" s="2" t="n">
-        <v>1778</v>
-      </c>
-      <c r="AD12" s="2" t="n">
-        <v>2011</v>
-      </c>
-      <c r="AE12" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="AF12" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="AG12" s="2" t="n">
-        <v>0.1158627548483342</v>
-      </c>
-      <c r="AH12" s="2" t="n">
-        <v>0.8841372451516658</v>
-      </c>
-      <c r="AI12" s="2" t="n">
-        <v>0.1158627548483342</v>
-      </c>
-      <c r="AJ12" s="2" t="n">
-        <v>0.8841372451516658</v>
-      </c>
-      <c r="AK12" s="2" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="B13" s="2" t="n"/>
-      <c r="C13" s="2" t="n">
-        <v>70</v>
-      </c>
-      <c r="D13" s="2" t="n">
-        <v>0.003094469740506609</v>
-      </c>
-      <c r="E13" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="F13" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="G13" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="H13" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="I13" s="2" t="n">
-        <v>61</v>
-      </c>
-      <c r="J13" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="K13" s="2" t="n">
-        <v>54</v>
-      </c>
-      <c r="L13" s="2" t="n">
-        <v>0.1147540983606557</v>
-      </c>
-      <c r="M13" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="N13" s="2" t="n">
-        <v>48925</v>
-      </c>
-      <c r="O13" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="P13" s="2" t="n">
-        <v>5708.02</v>
-      </c>
-      <c r="Q13" s="2" t="n">
-        <v>48925</v>
-      </c>
-      <c r="R13" s="2" t="n">
-        <v>0.1166687787429739</v>
-      </c>
-      <c r="S13" s="2" t="n">
-        <v>0.03969453341964182</v>
-      </c>
-      <c r="T13" s="2" t="n">
-        <v>1542.142857142857</v>
-      </c>
-      <c r="U13" s="2" t="n">
-        <v>853.9285714285714</v>
-      </c>
-      <c r="V13" s="2" t="n">
-        <v>1404.157857142857</v>
-      </c>
-      <c r="W13" s="2" t="n">
-        <v>1215.352666666667</v>
-      </c>
-      <c r="X13" s="2" t="n">
-        <v>5079.901047619047</v>
-      </c>
-      <c r="Y13" s="2" t="n">
-        <v>70</v>
-      </c>
-      <c r="Z13" s="2" t="n">
-        <v>70</v>
-      </c>
-      <c r="AA13" s="2" t="n">
-        <v>70</v>
-      </c>
-      <c r="AB13" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="AC13" s="2" t="n">
-        <v>66</v>
-      </c>
-      <c r="AD13" s="2" t="n">
-        <v>70</v>
-      </c>
-      <c r="AE13" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="AF13" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="AG13" s="2" t="n">
-        <v>0.05714285714285714</v>
-      </c>
-      <c r="AH13" s="2" t="n">
-        <v>0.9428571428571428</v>
-      </c>
-      <c r="AI13" s="2" t="n">
-        <v>0.05714285714285714</v>
-      </c>
-      <c r="AJ13" s="2" t="n">
-        <v>0.9428571428571428</v>
-      </c>
-      <c r="AK13" s="2" t="n">
         <v>1</v>
       </c>
     </row>
@@ -8387,6 +7231,570 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="25" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="21" customWidth="1" min="3" max="3"/>
+    <col width="25" customWidth="1" min="4" max="4"/>
+    <col width="23" customWidth="1" min="5" max="5"/>
+    <col width="24" customWidth="1" min="6" max="6"/>
+    <col width="24" customWidth="1" min="7" max="7"/>
+    <col width="24" customWidth="1" min="8" max="8"/>
+    <col width="22" customWidth="1" min="9" max="9"/>
+    <col width="23" customWidth="1" min="10" max="10"/>
+    <col width="23" customWidth="1" min="11" max="11"/>
+    <col width="32" customWidth="1" min="12" max="12"/>
+    <col width="32" customWidth="1" min="13" max="13"/>
+    <col width="32" customWidth="1" min="14" max="14"/>
+    <col width="32" customWidth="1" min="15" max="15"/>
+    <col width="32" customWidth="1" min="16" max="16"/>
+    <col width="32" customWidth="1" min="17" max="17"/>
+    <col width="21" customWidth="1" min="18" max="18"/>
+    <col width="27" customWidth="1" min="19" max="19"/>
+    <col width="20" customWidth="1" min="20" max="20"/>
+    <col width="20" customWidth="1" min="21" max="21"/>
+    <col width="20" customWidth="1" min="22" max="22"/>
+    <col width="19" customWidth="1" min="23" max="23"/>
+    <col width="11" customWidth="1" min="24" max="24"/>
+    <col width="27" customWidth="1" min="25" max="25"/>
+    <col width="26" customWidth="1" min="26" max="26"/>
+    <col width="31" customWidth="1" min="27" max="27"/>
+    <col width="32" customWidth="1" min="28" max="28"/>
+    <col width="17" customWidth="1" min="29" max="29"/>
+    <col width="17" customWidth="1" min="30" max="30"/>
+    <col width="15" customWidth="1" min="31" max="31"/>
+    <col width="21" customWidth="1" min="32" max="32"/>
+    <col width="22" customWidth="1" min="33" max="33"/>
+    <col width="21" customWidth="1" min="34" max="34"/>
+    <col width="23" customWidth="1" min="35" max="35"/>
+    <col width="11" customWidth="1" min="36" max="36"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>primary_model_score_bin</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>sample_cnt</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>sample_pct</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>duedate_3m_30_valid_cnt</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>duedate_3m_30_bad_cnt</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>duedate_3m_30_good_cnt</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>duedate_3m_30_bad_rate</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>duedate_1m_5_valid_cnt</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>duedate_1m_5_bad_cnt</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>duedate_1m_5_good_cnt</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>duedate_1m_5_bad_rate</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>duedate_3m_30_amount_overdue_amount</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>duedate_3m_30_amount_principal_amount</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>duedate_3m_30_amount_overdue_rate</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>duedate_1m_5_amount_overdue_amount</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>duedate_1m_5_amount_principal_amount</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>duedate_1m_5_amount_overdue_rate</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>avg_PTI</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>avg_requested_loan_amount</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>avg_total_amount</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>avg_gross_surplus</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>avg_net_surplus</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>avg_total_income</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>apply_cnt</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>completed_application_cnt</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>approved_application_cnt</t>
+        </is>
+      </c>
+      <c r="AA1" s="1" t="inlineStr">
+        <is>
+          <t>auto_approved_application_cnt</t>
+        </is>
+      </c>
+      <c r="AB1" s="1" t="inlineStr">
+        <is>
+          <t>manual_approved_application_cnt</t>
+        </is>
+      </c>
+      <c r="AC1" s="1" t="inlineStr">
+        <is>
+          <t>deal_sample_cnt</t>
+        </is>
+      </c>
+      <c r="AD1" s="1" t="inlineStr">
+        <is>
+          <t>completion_rate</t>
+        </is>
+      </c>
+      <c r="AE1" s="1" t="inlineStr">
+        <is>
+          <t>approval_rate</t>
+        </is>
+      </c>
+      <c r="AF1" s="1" t="inlineStr">
+        <is>
+          <t>auto_approval_rate</t>
+        </is>
+      </c>
+      <c r="AG1" s="1" t="inlineStr">
+        <is>
+          <t>manual_approval_rate</t>
+        </is>
+      </c>
+      <c r="AH1" s="1" t="inlineStr">
+        <is>
+          <t>auto_approval_share</t>
+        </is>
+      </c>
+      <c r="AI1" s="1" t="inlineStr">
+        <is>
+          <t>manual_approval_share</t>
+        </is>
+      </c>
+      <c r="AJ1" s="1" t="inlineStr">
+        <is>
+          <t>deal_rate</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" s="2" t="n">
+        <v>36</v>
+      </c>
+      <c r="C2" s="2" t="n">
+        <v>0.3636363636363636</v>
+      </c>
+      <c r="D2" s="2" t="n">
+        <v>29</v>
+      </c>
+      <c r="E2" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F2" s="2" t="n">
+        <v>29</v>
+      </c>
+      <c r="G2" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H2" s="2" t="n">
+        <v>35</v>
+      </c>
+      <c r="I2" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J2" s="2" t="n">
+        <v>35</v>
+      </c>
+      <c r="K2" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L2" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M2" s="2" t="n">
+        <v>38625</v>
+      </c>
+      <c r="N2" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O2" s="2" t="n">
+        <v>1068.43</v>
+      </c>
+      <c r="P2" s="2" t="n">
+        <v>38625</v>
+      </c>
+      <c r="Q2" s="2" t="n">
+        <v>0.02766161812297735</v>
+      </c>
+      <c r="R2" s="2" t="n">
+        <v>0.06203178427401005</v>
+      </c>
+      <c r="S2" s="2" t="n">
+        <v>2452.777777777778</v>
+      </c>
+      <c r="T2" s="2" t="n">
+        <v>1239.583333333333</v>
+      </c>
+      <c r="U2" s="2" t="n">
+        <v>2162.472962962963</v>
+      </c>
+      <c r="V2" s="2" t="n">
+        <v>1725.757824074074</v>
+      </c>
+      <c r="W2" s="2" t="n">
+        <v>7329.088240740742</v>
+      </c>
+      <c r="X2" s="2" t="n">
+        <v>36</v>
+      </c>
+      <c r="Y2" s="2" t="n">
+        <v>36</v>
+      </c>
+      <c r="Z2" s="2" t="n">
+        <v>36</v>
+      </c>
+      <c r="AA2" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="AB2" s="2" t="n">
+        <v>21</v>
+      </c>
+      <c r="AC2" s="2" t="n">
+        <v>36</v>
+      </c>
+      <c r="AD2" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE2" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF2" s="2" t="n">
+        <v>0.4166666666666667</v>
+      </c>
+      <c r="AG2" s="2" t="n">
+        <v>0.5833333333333334</v>
+      </c>
+      <c r="AH2" s="2" t="n">
+        <v>0.4166666666666667</v>
+      </c>
+      <c r="AI2" s="2" t="n">
+        <v>0.5833333333333334</v>
+      </c>
+      <c r="AJ2" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" s="2" t="n">
+        <v>40</v>
+      </c>
+      <c r="C3" s="2" t="n">
+        <v>0.404040404040404</v>
+      </c>
+      <c r="D3" s="2" t="n">
+        <v>35</v>
+      </c>
+      <c r="E3" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="F3" s="2" t="n">
+        <v>33</v>
+      </c>
+      <c r="G3" s="2" t="n">
+        <v>0.05714285714285714</v>
+      </c>
+      <c r="H3" s="2" t="n">
+        <v>40</v>
+      </c>
+      <c r="I3" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J3" s="2" t="n">
+        <v>39</v>
+      </c>
+      <c r="K3" s="2" t="n">
+        <v>0.025</v>
+      </c>
+      <c r="L3" s="2" t="n">
+        <v>2945.06</v>
+      </c>
+      <c r="M3" s="2" t="n">
+        <v>37725</v>
+      </c>
+      <c r="N3" s="2" t="n">
+        <v>0.07806653412856196</v>
+      </c>
+      <c r="O3" s="2" t="n">
+        <v>3000.56</v>
+      </c>
+      <c r="P3" s="2" t="n">
+        <v>37725</v>
+      </c>
+      <c r="Q3" s="2" t="n">
+        <v>0.0795377070907886</v>
+      </c>
+      <c r="R3" s="2" t="n">
+        <v>0.05924728981713567</v>
+      </c>
+      <c r="S3" s="2" t="n">
+        <v>2186.25</v>
+      </c>
+      <c r="T3" s="2" t="n">
+        <v>943.125</v>
+      </c>
+      <c r="U3" s="2" t="n">
+        <v>1753.214666666667</v>
+      </c>
+      <c r="V3" s="2" t="n">
+        <v>1411.317916666666</v>
+      </c>
+      <c r="W3" s="2" t="n">
+        <v>6191.864791666666</v>
+      </c>
+      <c r="X3" s="2" t="n">
+        <v>40</v>
+      </c>
+      <c r="Y3" s="2" t="n">
+        <v>40</v>
+      </c>
+      <c r="Z3" s="2" t="n">
+        <v>40</v>
+      </c>
+      <c r="AA3" s="2" t="n">
+        <v>22</v>
+      </c>
+      <c r="AB3" s="2" t="n">
+        <v>18</v>
+      </c>
+      <c r="AC3" s="2" t="n">
+        <v>40</v>
+      </c>
+      <c r="AD3" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE3" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF3" s="2" t="n">
+        <v>0.55</v>
+      </c>
+      <c r="AG3" s="2" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="AH3" s="2" t="n">
+        <v>0.55</v>
+      </c>
+      <c r="AI3" s="2" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="AJ3" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" s="2" t="n">
+        <v>23</v>
+      </c>
+      <c r="C4" s="2" t="n">
+        <v>0.2323232323232323</v>
+      </c>
+      <c r="D4" s="2" t="n">
+        <v>22</v>
+      </c>
+      <c r="E4" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="F4" s="2" t="n">
+        <v>19</v>
+      </c>
+      <c r="G4" s="2" t="n">
+        <v>0.1363636363636364</v>
+      </c>
+      <c r="H4" s="2" t="n">
+        <v>23</v>
+      </c>
+      <c r="I4" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="J4" s="2" t="n">
+        <v>20</v>
+      </c>
+      <c r="K4" s="2" t="n">
+        <v>0.1304347826086956</v>
+      </c>
+      <c r="L4" s="2" t="n">
+        <v>1495.57</v>
+      </c>
+      <c r="M4" s="2" t="n">
+        <v>17750</v>
+      </c>
+      <c r="N4" s="2" t="n">
+        <v>0.08425746478873239</v>
+      </c>
+      <c r="O4" s="2" t="n">
+        <v>2122.93</v>
+      </c>
+      <c r="P4" s="2" t="n">
+        <v>17750</v>
+      </c>
+      <c r="Q4" s="2" t="n">
+        <v>0.1196016901408451</v>
+      </c>
+      <c r="R4" s="2" t="n">
+        <v>0.05683708696921964</v>
+      </c>
+      <c r="S4" s="2" t="n">
+        <v>1943.478260869565</v>
+      </c>
+      <c r="T4" s="2" t="n">
+        <v>771.7391304347826</v>
+      </c>
+      <c r="U4" s="2" t="n">
+        <v>1902.294710144928</v>
+      </c>
+      <c r="V4" s="2" t="n">
+        <v>1618.030869565217</v>
+      </c>
+      <c r="W4" s="2" t="n">
+        <v>5643.044710144927</v>
+      </c>
+      <c r="X4" s="2" t="n">
+        <v>23</v>
+      </c>
+      <c r="Y4" s="2" t="n">
+        <v>23</v>
+      </c>
+      <c r="Z4" s="2" t="n">
+        <v>23</v>
+      </c>
+      <c r="AA4" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="AB4" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="AC4" s="2" t="n">
+        <v>23</v>
+      </c>
+      <c r="AD4" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE4" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF4" s="2" t="n">
+        <v>0.3478260869565217</v>
+      </c>
+      <c r="AG4" s="2" t="n">
+        <v>0.6521739130434783</v>
+      </c>
+      <c r="AH4" s="2" t="n">
+        <v>0.3478260869565217</v>
+      </c>
+      <c r="AI4" s="2" t="n">
+        <v>0.6521739130434783</v>
+      </c>
+      <c r="AJ4" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:AJ4"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="28" customWidth="1" min="1" max="1"/>
     <col width="12" customWidth="1" min="2" max="2"/>
     <col width="21" customWidth="1" min="3" max="3"/>
     <col width="25" customWidth="1" min="4" max="4"/>
@@ -8427,7 +7835,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>primary_model_score_bin</t>
+          <t>comparison_model_score_bin</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
@@ -8611,88 +8019,88 @@
         <v>1</v>
       </c>
       <c r="B2" s="2" t="n">
-        <v>8739</v>
+        <v>47</v>
       </c>
       <c r="C2" s="2" t="n">
-        <v>0.3863224437469608</v>
+        <v>0.4747474747474748</v>
       </c>
       <c r="D2" s="2" t="n">
-        <v>4647</v>
+        <v>39</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>380</v>
+        <v>0</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>4267</v>
+        <v>39</v>
       </c>
       <c r="G2" s="2" t="n">
-        <v>0.08177318700236712</v>
+        <v>0</v>
       </c>
       <c r="H2" s="2" t="n">
-        <v>8167</v>
+        <v>46</v>
       </c>
       <c r="I2" s="2" t="n">
-        <v>353</v>
+        <v>0</v>
       </c>
       <c r="J2" s="2" t="n">
-        <v>7814</v>
+        <v>46</v>
       </c>
       <c r="K2" s="2" t="n">
-        <v>0.04322272560303661</v>
+        <v>0</v>
       </c>
       <c r="L2" s="2" t="n">
-        <v>428991.3199999999</v>
+        <v>0</v>
       </c>
       <c r="M2" s="2" t="n">
-        <v>10431095</v>
+        <v>47150</v>
       </c>
       <c r="N2" s="2" t="n">
-        <v>0.04112620199509255</v>
+        <v>0</v>
       </c>
       <c r="O2" s="2" t="n">
-        <v>613663.5000000001</v>
+        <v>1068.43</v>
       </c>
       <c r="P2" s="2" t="n">
-        <v>10431095</v>
+        <v>47150</v>
       </c>
       <c r="Q2" s="2" t="n">
-        <v>0.05883020910077035</v>
+        <v>0.02266023329798516</v>
       </c>
       <c r="R2" s="2" t="n">
-        <v>0.0500339325222459</v>
+        <v>0.06091122931593518</v>
       </c>
       <c r="S2" s="2" t="n">
-        <v>2466.796773086166</v>
+        <v>2168.617021276596</v>
       </c>
       <c r="T2" s="2" t="n">
-        <v>1391.057901361712</v>
+        <v>1130.851063829787</v>
       </c>
       <c r="U2" s="2" t="n">
-        <v>2226.247654575275</v>
+        <v>1797.775531914893</v>
       </c>
       <c r="V2" s="2" t="n">
-        <v>1845.225690010298</v>
+        <v>1399.102872340425</v>
       </c>
       <c r="W2" s="2" t="n">
-        <v>8179.891385551359</v>
+        <v>6880.418723404256</v>
       </c>
       <c r="X2" s="2" t="n">
-        <v>8739</v>
+        <v>47</v>
       </c>
       <c r="Y2" s="2" t="n">
-        <v>8739</v>
+        <v>47</v>
       </c>
       <c r="Z2" s="2" t="n">
-        <v>8739</v>
+        <v>47</v>
       </c>
       <c r="AA2" s="2" t="n">
-        <v>2765</v>
+        <v>19</v>
       </c>
       <c r="AB2" s="2" t="n">
-        <v>5974</v>
+        <v>28</v>
       </c>
       <c r="AC2" s="2" t="n">
-        <v>8739</v>
+        <v>47</v>
       </c>
       <c r="AD2" s="2" t="n">
         <v>1</v>
@@ -8701,16 +8109,16 @@
         <v>1</v>
       </c>
       <c r="AF2" s="2" t="n">
-        <v>0.3163977571804554</v>
+        <v>0.4042553191489361</v>
       </c>
       <c r="AG2" s="2" t="n">
-        <v>0.6836022428195446</v>
+        <v>0.5957446808510638</v>
       </c>
       <c r="AH2" s="2" t="n">
-        <v>0.3163977571804554</v>
+        <v>0.4042553191489361</v>
       </c>
       <c r="AI2" s="2" t="n">
-        <v>0.6836022428195446</v>
+        <v>0.5957446808510638</v>
       </c>
       <c r="AJ2" s="2" t="n">
         <v>1</v>
@@ -8721,88 +8129,88 @@
         <v>2</v>
       </c>
       <c r="B3" s="2" t="n">
-        <v>9381</v>
+        <v>34</v>
       </c>
       <c r="C3" s="2" t="n">
-        <v>0.4147031519384642</v>
+        <v>0.3434343434343434</v>
       </c>
       <c r="D3" s="2" t="n">
-        <v>5088</v>
+        <v>30</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>660</v>
+        <v>2</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>4428</v>
+        <v>28</v>
       </c>
       <c r="G3" s="2" t="n">
-        <v>0.1297169811320755</v>
+        <v>0.06666666666666667</v>
       </c>
       <c r="H3" s="2" t="n">
-        <v>8701</v>
+        <v>34</v>
       </c>
       <c r="I3" s="2" t="n">
-        <v>618</v>
+        <v>2</v>
       </c>
       <c r="J3" s="2" t="n">
-        <v>8083</v>
+        <v>32</v>
       </c>
       <c r="K3" s="2" t="n">
-        <v>0.07102631881392943</v>
+        <v>0.05882352941176471</v>
       </c>
       <c r="L3" s="2" t="n">
-        <v>560936.97</v>
+        <v>2945.06</v>
       </c>
       <c r="M3" s="2" t="n">
-        <v>8014685</v>
+        <v>33075</v>
       </c>
       <c r="N3" s="2" t="n">
-        <v>0.06998864833739567</v>
+        <v>0.08904187452758881</v>
       </c>
       <c r="O3" s="2" t="n">
-        <v>744347.4099999999</v>
+        <v>2647.62</v>
       </c>
       <c r="P3" s="2" t="n">
-        <v>8014685</v>
+        <v>33075</v>
       </c>
       <c r="Q3" s="2" t="n">
-        <v>0.0928729463478602</v>
+        <v>0.08004897959183672</v>
       </c>
       <c r="R3" s="2" t="n">
-        <v>0.04556513622544672</v>
+        <v>0.05958713495103481</v>
       </c>
       <c r="S3" s="2" t="n">
-        <v>2047.330774970686</v>
+        <v>2637.5</v>
       </c>
       <c r="T3" s="2" t="n">
-        <v>1005.827736915041</v>
+        <v>972.7941176470588</v>
       </c>
       <c r="U3" s="2" t="n">
-        <v>1597.240826493266</v>
+        <v>2142.047598039215</v>
       </c>
       <c r="V3" s="2" t="n">
-        <v>1336.839326830828</v>
+        <v>1798.678725490196</v>
       </c>
       <c r="W3" s="2" t="n">
-        <v>6105.452577550367</v>
+        <v>6358.617352941175</v>
       </c>
       <c r="X3" s="2" t="n">
-        <v>9381</v>
+        <v>34</v>
       </c>
       <c r="Y3" s="2" t="n">
-        <v>9381</v>
+        <v>34</v>
       </c>
       <c r="Z3" s="2" t="n">
-        <v>9381</v>
+        <v>34</v>
       </c>
       <c r="AA3" s="2" t="n">
-        <v>2850</v>
+        <v>17</v>
       </c>
       <c r="AB3" s="2" t="n">
-        <v>6531</v>
+        <v>17</v>
       </c>
       <c r="AC3" s="2" t="n">
-        <v>9381</v>
+        <v>34</v>
       </c>
       <c r="AD3" s="2" t="n">
         <v>1</v>
@@ -8811,16 +8219,16 @@
         <v>1</v>
       </c>
       <c r="AF3" s="2" t="n">
-        <v>0.3038055644387592</v>
+        <v>0.5</v>
       </c>
       <c r="AG3" s="2" t="n">
-        <v>0.6961944355612408</v>
+        <v>0.5</v>
       </c>
       <c r="AH3" s="2" t="n">
-        <v>0.3038055644387592</v>
+        <v>0.5</v>
       </c>
       <c r="AI3" s="2" t="n">
-        <v>0.6961944355612408</v>
+        <v>0.5</v>
       </c>
       <c r="AJ3" s="2" t="n">
         <v>1</v>
@@ -8831,88 +8239,88 @@
         <v>3</v>
       </c>
       <c r="B4" s="2" t="n">
-        <v>4501</v>
+        <v>18</v>
       </c>
       <c r="C4" s="2" t="n">
-        <v>0.1989744043145749</v>
+        <v>0.1818181818181818</v>
       </c>
       <c r="D4" s="2" t="n">
-        <v>2615</v>
+        <v>17</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>589</v>
+        <v>3</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>2026</v>
+        <v>14</v>
       </c>
       <c r="G4" s="2" t="n">
-        <v>0.2252390057361377</v>
+        <v>0.1764705882352941</v>
       </c>
       <c r="H4" s="2" t="n">
-        <v>4277</v>
+        <v>18</v>
       </c>
       <c r="I4" s="2" t="n">
-        <v>508</v>
+        <v>2</v>
       </c>
       <c r="J4" s="2" t="n">
-        <v>3769</v>
+        <v>16</v>
       </c>
       <c r="K4" s="2" t="n">
-        <v>0.1187748421790975</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="L4" s="2" t="n">
-        <v>392401.15</v>
+        <v>1495.57</v>
       </c>
       <c r="M4" s="2" t="n">
-        <v>3029912</v>
+        <v>13875</v>
       </c>
       <c r="N4" s="2" t="n">
-        <v>0.1295090913531482</v>
+        <v>0.1077888288288288</v>
       </c>
       <c r="O4" s="2" t="n">
-        <v>508979.38</v>
+        <v>2475.87</v>
       </c>
       <c r="P4" s="2" t="n">
-        <v>3029912</v>
+        <v>13875</v>
       </c>
       <c r="Q4" s="2" t="n">
-        <v>0.1679848721679046</v>
+        <v>0.1784410810810811</v>
       </c>
       <c r="R4" s="2" t="n">
-        <v>0.03915502894409028</v>
+        <v>0.05674991448098357</v>
       </c>
       <c r="S4" s="2" t="n">
-        <v>1770.634747833815</v>
+        <v>1602.777777777778</v>
       </c>
       <c r="T4" s="2" t="n">
-        <v>757.1621861808487</v>
+        <v>770.8333333333334</v>
       </c>
       <c r="U4" s="2" t="n">
-        <v>1411.360702436496</v>
+        <v>1911.406851851852</v>
       </c>
       <c r="V4" s="2" t="n">
-        <v>1219.821660001481</v>
+        <v>1604.544259259259</v>
       </c>
       <c r="W4" s="2" t="n">
-        <v>5205.221994001333</v>
+        <v>5652.173703703704</v>
       </c>
       <c r="X4" s="2" t="n">
-        <v>4501</v>
+        <v>18</v>
       </c>
       <c r="Y4" s="2" t="n">
-        <v>4501</v>
+        <v>18</v>
       </c>
       <c r="Z4" s="2" t="n">
-        <v>4501</v>
+        <v>18</v>
       </c>
       <c r="AA4" s="2" t="n">
-        <v>863</v>
+        <v>9</v>
       </c>
       <c r="AB4" s="2" t="n">
-        <v>3638</v>
+        <v>9</v>
       </c>
       <c r="AC4" s="2" t="n">
-        <v>4501</v>
+        <v>18</v>
       </c>
       <c r="AD4" s="2" t="n">
         <v>1</v>
@@ -8921,690 +8329,18 @@
         <v>1</v>
       </c>
       <c r="AF4" s="2" t="n">
-        <v>0.1917351699622306</v>
+        <v>0.5</v>
       </c>
       <c r="AG4" s="2" t="n">
-        <v>0.8082648300377694</v>
+        <v>0.5</v>
       </c>
       <c r="AH4" s="2" t="n">
-        <v>0.1917351699622306</v>
+        <v>0.5</v>
       </c>
       <c r="AI4" s="2" t="n">
-        <v>0.8082648300377694</v>
+        <v>0.5</v>
       </c>
       <c r="AJ4" s="2" t="n">
-        <v>1</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:AJ5"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="28" customWidth="1" min="1" max="1"/>
-    <col width="12" customWidth="1" min="2" max="2"/>
-    <col width="21" customWidth="1" min="3" max="3"/>
-    <col width="25" customWidth="1" min="4" max="4"/>
-    <col width="23" customWidth="1" min="5" max="5"/>
-    <col width="24" customWidth="1" min="6" max="6"/>
-    <col width="24" customWidth="1" min="7" max="7"/>
-    <col width="24" customWidth="1" min="8" max="8"/>
-    <col width="22" customWidth="1" min="9" max="9"/>
-    <col width="23" customWidth="1" min="10" max="10"/>
-    <col width="23" customWidth="1" min="11" max="11"/>
-    <col width="32" customWidth="1" min="12" max="12"/>
-    <col width="32" customWidth="1" min="13" max="13"/>
-    <col width="32" customWidth="1" min="14" max="14"/>
-    <col width="32" customWidth="1" min="15" max="15"/>
-    <col width="32" customWidth="1" min="16" max="16"/>
-    <col width="32" customWidth="1" min="17" max="17"/>
-    <col width="21" customWidth="1" min="18" max="18"/>
-    <col width="27" customWidth="1" min="19" max="19"/>
-    <col width="20" customWidth="1" min="20" max="20"/>
-    <col width="20" customWidth="1" min="21" max="21"/>
-    <col width="20" customWidth="1" min="22" max="22"/>
-    <col width="20" customWidth="1" min="23" max="23"/>
-    <col width="11" customWidth="1" min="24" max="24"/>
-    <col width="27" customWidth="1" min="25" max="25"/>
-    <col width="26" customWidth="1" min="26" max="26"/>
-    <col width="31" customWidth="1" min="27" max="27"/>
-    <col width="32" customWidth="1" min="28" max="28"/>
-    <col width="17" customWidth="1" min="29" max="29"/>
-    <col width="17" customWidth="1" min="30" max="30"/>
-    <col width="15" customWidth="1" min="31" max="31"/>
-    <col width="20" customWidth="1" min="32" max="32"/>
-    <col width="22" customWidth="1" min="33" max="33"/>
-    <col width="21" customWidth="1" min="34" max="34"/>
-    <col width="23" customWidth="1" min="35" max="35"/>
-    <col width="11" customWidth="1" min="36" max="36"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>comparison_model_score_bin</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>sample_cnt</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>sample_pct</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>duedate_3m_30_valid_cnt</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>duedate_3m_30_bad_cnt</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>duedate_3m_30_good_cnt</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>duedate_3m_30_bad_rate</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>duedate_1m_5_valid_cnt</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t>duedate_1m_5_bad_cnt</t>
-        </is>
-      </c>
-      <c r="J1" s="1" t="inlineStr">
-        <is>
-          <t>duedate_1m_5_good_cnt</t>
-        </is>
-      </c>
-      <c r="K1" s="1" t="inlineStr">
-        <is>
-          <t>duedate_1m_5_bad_rate</t>
-        </is>
-      </c>
-      <c r="L1" s="1" t="inlineStr">
-        <is>
-          <t>duedate_3m_30_amount_overdue_amount</t>
-        </is>
-      </c>
-      <c r="M1" s="1" t="inlineStr">
-        <is>
-          <t>duedate_3m_30_amount_principal_amount</t>
-        </is>
-      </c>
-      <c r="N1" s="1" t="inlineStr">
-        <is>
-          <t>duedate_3m_30_amount_overdue_rate</t>
-        </is>
-      </c>
-      <c r="O1" s="1" t="inlineStr">
-        <is>
-          <t>duedate_1m_5_amount_overdue_amount</t>
-        </is>
-      </c>
-      <c r="P1" s="1" t="inlineStr">
-        <is>
-          <t>duedate_1m_5_amount_principal_amount</t>
-        </is>
-      </c>
-      <c r="Q1" s="1" t="inlineStr">
-        <is>
-          <t>duedate_1m_5_amount_overdue_rate</t>
-        </is>
-      </c>
-      <c r="R1" s="1" t="inlineStr">
-        <is>
-          <t>avg_PTI</t>
-        </is>
-      </c>
-      <c r="S1" s="1" t="inlineStr">
-        <is>
-          <t>avg_requested_loan_amount</t>
-        </is>
-      </c>
-      <c r="T1" s="1" t="inlineStr">
-        <is>
-          <t>avg_total_amount</t>
-        </is>
-      </c>
-      <c r="U1" s="1" t="inlineStr">
-        <is>
-          <t>avg_gross_surplus</t>
-        </is>
-      </c>
-      <c r="V1" s="1" t="inlineStr">
-        <is>
-          <t>avg_net_surplus</t>
-        </is>
-      </c>
-      <c r="W1" s="1" t="inlineStr">
-        <is>
-          <t>avg_total_income</t>
-        </is>
-      </c>
-      <c r="X1" s="1" t="inlineStr">
-        <is>
-          <t>apply_cnt</t>
-        </is>
-      </c>
-      <c r="Y1" s="1" t="inlineStr">
-        <is>
-          <t>completed_application_cnt</t>
-        </is>
-      </c>
-      <c r="Z1" s="1" t="inlineStr">
-        <is>
-          <t>approved_application_cnt</t>
-        </is>
-      </c>
-      <c r="AA1" s="1" t="inlineStr">
-        <is>
-          <t>auto_approved_application_cnt</t>
-        </is>
-      </c>
-      <c r="AB1" s="1" t="inlineStr">
-        <is>
-          <t>manual_approved_application_cnt</t>
-        </is>
-      </c>
-      <c r="AC1" s="1" t="inlineStr">
-        <is>
-          <t>deal_sample_cnt</t>
-        </is>
-      </c>
-      <c r="AD1" s="1" t="inlineStr">
-        <is>
-          <t>completion_rate</t>
-        </is>
-      </c>
-      <c r="AE1" s="1" t="inlineStr">
-        <is>
-          <t>approval_rate</t>
-        </is>
-      </c>
-      <c r="AF1" s="1" t="inlineStr">
-        <is>
-          <t>auto_approval_rate</t>
-        </is>
-      </c>
-      <c r="AG1" s="1" t="inlineStr">
-        <is>
-          <t>manual_approval_rate</t>
-        </is>
-      </c>
-      <c r="AH1" s="1" t="inlineStr">
-        <is>
-          <t>auto_approval_share</t>
-        </is>
-      </c>
-      <c r="AI1" s="1" t="inlineStr">
-        <is>
-          <t>manual_approval_share</t>
-        </is>
-      </c>
-      <c r="AJ1" s="1" t="inlineStr">
-        <is>
-          <t>deal_rate</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="B2" s="2" t="n">
-        <v>9155</v>
-      </c>
-      <c r="C2" s="2" t="n">
-        <v>0.4047124353476858</v>
-      </c>
-      <c r="D2" s="2" t="n">
-        <v>4434</v>
-      </c>
-      <c r="E2" s="2" t="n">
-        <v>305</v>
-      </c>
-      <c r="F2" s="2" t="n">
-        <v>4129</v>
-      </c>
-      <c r="G2" s="2" t="n">
-        <v>0.06878664862426703</v>
-      </c>
-      <c r="H2" s="2" t="n">
-        <v>8417</v>
-      </c>
-      <c r="I2" s="2" t="n">
-        <v>298</v>
-      </c>
-      <c r="J2" s="2" t="n">
-        <v>8119</v>
-      </c>
-      <c r="K2" s="2" t="n">
-        <v>0.03540453843412142</v>
-      </c>
-      <c r="L2" s="2" t="n">
-        <v>292961.7</v>
-      </c>
-      <c r="M2" s="2" t="n">
-        <v>9809571</v>
-      </c>
-      <c r="N2" s="2" t="n">
-        <v>0.02986488399951435</v>
-      </c>
-      <c r="O2" s="2" t="n">
-        <v>455244.76</v>
-      </c>
-      <c r="P2" s="2" t="n">
-        <v>9809571</v>
-      </c>
-      <c r="Q2" s="2" t="n">
-        <v>0.04640822315267405</v>
-      </c>
-      <c r="R2" s="2" t="n">
-        <v>0.05029340897260857</v>
-      </c>
-      <c r="S2" s="2" t="n">
-        <v>2258.309666848716</v>
-      </c>
-      <c r="T2" s="2" t="n">
-        <v>1315.055270344074</v>
-      </c>
-      <c r="U2" s="2" t="n">
-        <v>1669.640882941926</v>
-      </c>
-      <c r="V2" s="2" t="n">
-        <v>1330.168427635172</v>
-      </c>
-      <c r="W2" s="2" t="n">
-        <v>7144.923472783542</v>
-      </c>
-      <c r="X2" s="2" t="n">
-        <v>9155</v>
-      </c>
-      <c r="Y2" s="2" t="n">
-        <v>9155</v>
-      </c>
-      <c r="Z2" s="2" t="n">
-        <v>9155</v>
-      </c>
-      <c r="AA2" s="2" t="n">
-        <v>2769</v>
-      </c>
-      <c r="AB2" s="2" t="n">
-        <v>6386</v>
-      </c>
-      <c r="AC2" s="2" t="n">
-        <v>9155</v>
-      </c>
-      <c r="AD2" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="AE2" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="AF2" s="2" t="n">
-        <v>0.3024576734025123</v>
-      </c>
-      <c r="AG2" s="2" t="n">
-        <v>0.6975423265974877</v>
-      </c>
-      <c r="AH2" s="2" t="n">
-        <v>0.3024576734025123</v>
-      </c>
-      <c r="AI2" s="2" t="n">
-        <v>0.6975423265974877</v>
-      </c>
-      <c r="AJ2" s="2" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="B3" s="2" t="n">
-        <v>9224</v>
-      </c>
-      <c r="C3" s="2" t="n">
-        <v>0.4077626983776137</v>
-      </c>
-      <c r="D3" s="2" t="n">
-        <v>4845</v>
-      </c>
-      <c r="E3" s="2" t="n">
-        <v>653</v>
-      </c>
-      <c r="F3" s="2" t="n">
-        <v>4192</v>
-      </c>
-      <c r="G3" s="2" t="n">
-        <v>0.1347781217750258</v>
-      </c>
-      <c r="H3" s="2" t="n">
-        <v>8530</v>
-      </c>
-      <c r="I3" s="2" t="n">
-        <v>675</v>
-      </c>
-      <c r="J3" s="2" t="n">
-        <v>7855</v>
-      </c>
-      <c r="K3" s="2" t="n">
-        <v>0.07913247362250879</v>
-      </c>
-      <c r="L3" s="2" t="n">
-        <v>571519.86</v>
-      </c>
-      <c r="M3" s="2" t="n">
-        <v>7747774</v>
-      </c>
-      <c r="N3" s="2" t="n">
-        <v>0.07376568547301457</v>
-      </c>
-      <c r="O3" s="2" t="n">
-        <v>764604.49</v>
-      </c>
-      <c r="P3" s="2" t="n">
-        <v>7747774</v>
-      </c>
-      <c r="Q3" s="2" t="n">
-        <v>0.09868698932106176</v>
-      </c>
-      <c r="R3" s="2" t="n">
-        <v>0.04415730029478754</v>
-      </c>
-      <c r="S3" s="2" t="n">
-        <v>2105.131613183001</v>
-      </c>
-      <c r="T3" s="2" t="n">
-        <v>972.6863616652212</v>
-      </c>
-      <c r="U3" s="2" t="n">
-        <v>1829.891354799075</v>
-      </c>
-      <c r="V3" s="2" t="n">
-        <v>1560.897386166522</v>
-      </c>
-      <c r="W3" s="2" t="n">
-        <v>6460.055926206996</v>
-      </c>
-      <c r="X3" s="2" t="n">
-        <v>9224</v>
-      </c>
-      <c r="Y3" s="2" t="n">
-        <v>9224</v>
-      </c>
-      <c r="Z3" s="2" t="n">
-        <v>9224</v>
-      </c>
-      <c r="AA3" s="2" t="n">
-        <v>2908</v>
-      </c>
-      <c r="AB3" s="2" t="n">
-        <v>6316</v>
-      </c>
-      <c r="AC3" s="2" t="n">
-        <v>9224</v>
-      </c>
-      <c r="AD3" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="AE3" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="AF3" s="2" t="n">
-        <v>0.3152645273200347</v>
-      </c>
-      <c r="AG3" s="2" t="n">
-        <v>0.6847354726799653</v>
-      </c>
-      <c r="AH3" s="2" t="n">
-        <v>0.3152645273200347</v>
-      </c>
-      <c r="AI3" s="2" t="n">
-        <v>0.6847354726799653</v>
-      </c>
-      <c r="AJ3" s="2" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="B4" s="2" t="n">
-        <v>3987</v>
-      </c>
-      <c r="C4" s="2" t="n">
-        <v>0.1762521550771407</v>
-      </c>
-      <c r="D4" s="2" t="n">
-        <v>3069</v>
-      </c>
-      <c r="E4" s="2" t="n">
-        <v>671</v>
-      </c>
-      <c r="F4" s="2" t="n">
-        <v>2398</v>
-      </c>
-      <c r="G4" s="2" t="n">
-        <v>0.2186379928315412</v>
-      </c>
-      <c r="H4" s="2" t="n">
-        <v>3987</v>
-      </c>
-      <c r="I4" s="2" t="n">
-        <v>492</v>
-      </c>
-      <c r="J4" s="2" t="n">
-        <v>3495</v>
-      </c>
-      <c r="K4" s="2" t="n">
-        <v>0.1234010534236268</v>
-      </c>
-      <c r="L4" s="2" t="n">
-        <v>517847.88</v>
-      </c>
-      <c r="M4" s="2" t="n">
-        <v>3670972</v>
-      </c>
-      <c r="N4" s="2" t="n">
-        <v>0.1410656033333951</v>
-      </c>
-      <c r="O4" s="2" t="n">
-        <v>639274.29</v>
-      </c>
-      <c r="P4" s="2" t="n">
-        <v>3670972</v>
-      </c>
-      <c r="Q4" s="2" t="n">
-        <v>0.1741430580238695</v>
-      </c>
-      <c r="R4" s="2" t="n">
-        <v>0.04039232457558297</v>
-      </c>
-      <c r="S4" s="2" t="n">
-        <v>2028.897667419112</v>
-      </c>
-      <c r="T4" s="2" t="n">
-        <v>920.7353900175571</v>
-      </c>
-      <c r="U4" s="2" t="n">
-        <v>2031.03079006772</v>
-      </c>
-      <c r="V4" s="2" t="n">
-        <v>1787.556734386757</v>
-      </c>
-      <c r="W4" s="2" t="n">
-        <v>6387.265431402056</v>
-      </c>
-      <c r="X4" s="2" t="n">
-        <v>3987</v>
-      </c>
-      <c r="Y4" s="2" t="n">
-        <v>3987</v>
-      </c>
-      <c r="Z4" s="2" t="n">
-        <v>3987</v>
-      </c>
-      <c r="AA4" s="2" t="n">
-        <v>760</v>
-      </c>
-      <c r="AB4" s="2" t="n">
-        <v>3227</v>
-      </c>
-      <c r="AC4" s="2" t="n">
-        <v>3987</v>
-      </c>
-      <c r="AD4" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="AE4" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="AF4" s="2" t="n">
-        <v>0.1906195134186105</v>
-      </c>
-      <c r="AG4" s="2" t="n">
-        <v>0.8093804865813895</v>
-      </c>
-      <c r="AH4" s="2" t="n">
-        <v>0.1906195134186105</v>
-      </c>
-      <c r="AI4" s="2" t="n">
-        <v>0.8093804865813895</v>
-      </c>
-      <c r="AJ4" s="2" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="2" t="n"/>
-      <c r="B5" s="2" t="n">
-        <v>255</v>
-      </c>
-      <c r="C5" s="2" t="n">
-        <v>0.01127271119755979</v>
-      </c>
-      <c r="D5" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="E5" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F5" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="G5" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="H5" s="2" t="n">
-        <v>211</v>
-      </c>
-      <c r="I5" s="2" t="n">
-        <v>14</v>
-      </c>
-      <c r="J5" s="2" t="n">
-        <v>197</v>
-      </c>
-      <c r="K5" s="2" t="n">
-        <v>0.06635071090047394</v>
-      </c>
-      <c r="L5" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="M5" s="2" t="n">
-        <v>247375</v>
-      </c>
-      <c r="N5" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="O5" s="2" t="n">
-        <v>7866.75</v>
-      </c>
-      <c r="P5" s="2" t="n">
-        <v>247375</v>
-      </c>
-      <c r="Q5" s="2" t="n">
-        <v>0.03180090955027792</v>
-      </c>
-      <c r="R5" s="2" t="n">
-        <v>0.04761791911361497</v>
-      </c>
-      <c r="S5" s="2" t="n">
-        <v>2161.56862745098</v>
-      </c>
-      <c r="T5" s="2" t="n">
-        <v>1246.078431372549</v>
-      </c>
-      <c r="U5" s="2" t="n">
-        <v>2075.408111111111</v>
-      </c>
-      <c r="V5" s="2" t="n">
-        <v>1781.710496732026</v>
-      </c>
-      <c r="W5" s="2" t="n">
-        <v>6755.561222222222</v>
-      </c>
-      <c r="X5" s="2" t="n">
-        <v>255</v>
-      </c>
-      <c r="Y5" s="2" t="n">
-        <v>255</v>
-      </c>
-      <c r="Z5" s="2" t="n">
-        <v>255</v>
-      </c>
-      <c r="AA5" s="2" t="n">
-        <v>41</v>
-      </c>
-      <c r="AB5" s="2" t="n">
-        <v>214</v>
-      </c>
-      <c r="AC5" s="2" t="n">
-        <v>255</v>
-      </c>
-      <c r="AD5" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="AE5" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="AF5" s="2" t="n">
-        <v>0.1607843137254902</v>
-      </c>
-      <c r="AG5" s="2" t="n">
-        <v>0.8392156862745098</v>
-      </c>
-      <c r="AH5" s="2" t="n">
-        <v>0.1607843137254902</v>
-      </c>
-      <c r="AI5" s="2" t="n">
-        <v>0.8392156862745098</v>
-      </c>
-      <c r="AJ5" s="2" t="n">
         <v>1</v>
       </c>
     </row>
@@ -9838,88 +8574,88 @@
     </row>
     <row r="2">
       <c r="A2" s="2" t="n">
-        <v>22621</v>
+        <v>99</v>
       </c>
       <c r="B2" s="2" t="n">
         <v>1</v>
       </c>
       <c r="C2" s="2" t="n">
-        <v>12350</v>
+        <v>86</v>
       </c>
       <c r="D2" s="2" t="n">
-        <v>1629</v>
+        <v>5</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>10721</v>
+        <v>81</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>0.1319028340080972</v>
+        <v>0.05813953488372093</v>
       </c>
       <c r="G2" s="2" t="n">
-        <v>21145</v>
+        <v>98</v>
       </c>
       <c r="H2" s="2" t="n">
-        <v>1479</v>
+        <v>4</v>
       </c>
       <c r="I2" s="2" t="n">
-        <v>19666</v>
+        <v>94</v>
       </c>
       <c r="J2" s="2" t="n">
-        <v>0.0699456136202412</v>
+        <v>0.04081632653061224</v>
       </c>
       <c r="K2" s="2" t="n">
-        <v>1382329.44</v>
+        <v>4440.63</v>
       </c>
       <c r="L2" s="2" t="n">
-        <v>21475692</v>
+        <v>94100</v>
       </c>
       <c r="M2" s="2" t="n">
-        <v>0.06436716637582621</v>
+        <v>0.04719054197662062</v>
       </c>
       <c r="N2" s="2" t="n">
-        <v>1866990.29</v>
+        <v>6191.92</v>
       </c>
       <c r="O2" s="2" t="n">
-        <v>21475692</v>
+        <v>94100</v>
       </c>
       <c r="P2" s="2" t="n">
-        <v>0.08693504684272806</v>
+        <v>0.06580148777895856</v>
       </c>
       <c r="Q2" s="2" t="n">
-        <v>0.04601608525353313</v>
+        <v>0.05969988713981658</v>
       </c>
       <c r="R2" s="2" t="n">
-        <v>2154.324477255647</v>
+        <v>2226.767676767677</v>
       </c>
       <c r="S2" s="2" t="n">
-        <v>1105.172715618231</v>
+        <v>1011.111111111111</v>
       </c>
       <c r="T2" s="2" t="n">
-        <v>1803.254894493317</v>
+        <v>1936.670622895623</v>
       </c>
       <c r="U2" s="2" t="n">
-        <v>1509.9568684703</v>
+        <v>1573.683922558922</v>
       </c>
       <c r="V2" s="2" t="n">
-        <v>6727.732003153411</v>
+        <v>6477.896936026937</v>
       </c>
       <c r="W2" s="2" t="n">
-        <v>22621</v>
+        <v>99</v>
       </c>
       <c r="X2" s="2" t="n">
-        <v>22621</v>
+        <v>99</v>
       </c>
       <c r="Y2" s="2" t="n">
-        <v>22621</v>
+        <v>99</v>
       </c>
       <c r="Z2" s="2" t="n">
-        <v>6478</v>
+        <v>45</v>
       </c>
       <c r="AA2" s="2" t="n">
-        <v>16143</v>
+        <v>54</v>
       </c>
       <c r="AB2" s="2" t="n">
-        <v>22621</v>
+        <v>99</v>
       </c>
       <c r="AC2" s="2" t="n">
         <v>1</v>
@@ -9928,16 +8664,16 @@
         <v>1</v>
       </c>
       <c r="AE2" s="2" t="n">
-        <v>0.2863710711285973</v>
+        <v>0.4545454545454545</v>
       </c>
       <c r="AF2" s="2" t="n">
-        <v>0.7136289288714027</v>
+        <v>0.5454545454545454</v>
       </c>
       <c r="AG2" s="2" t="n">
-        <v>0.2863710711285973</v>
+        <v>0.4545454545454545</v>
       </c>
       <c r="AH2" s="2" t="n">
-        <v>0.7136289288714027</v>
+        <v>0.5454545454545454</v>
       </c>
       <c r="AI2" s="2" t="n">
         <v>1</v>
